--- a/Carbon/Acidification.xlsx
+++ b/Carbon/Acidification.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lukawright/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luka/Desktop/PhD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB15661E-314B-9240-812E-3301478B3E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98219FA7-3F78-8542-8C07-36BB15E2FADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" xr2:uid="{EAD298CE-C7FF-3B4B-97C2-3F8F37547715}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{EAD298CE-C7FF-3B4B-97C2-3F8F37547715}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="718">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="1054">
   <si>
     <t>ID</t>
   </si>
@@ -2190,6 +2190,1014 @@
   </si>
   <si>
     <t>E_1_2_1</t>
+  </si>
+  <si>
+    <t>E_1_7_21</t>
+  </si>
+  <si>
+    <t>E_1_7_20</t>
+  </si>
+  <si>
+    <t>E_1_7_19</t>
+  </si>
+  <si>
+    <t>E_1_7_18</t>
+  </si>
+  <si>
+    <t>E_1_7_17</t>
+  </si>
+  <si>
+    <t>E_1_7_16</t>
+  </si>
+  <si>
+    <t>E_1_7_15</t>
+  </si>
+  <si>
+    <t>E_1_7_14</t>
+  </si>
+  <si>
+    <t>E_1_7_13</t>
+  </si>
+  <si>
+    <t>E_1_7_12</t>
+  </si>
+  <si>
+    <t>E_1_7_11</t>
+  </si>
+  <si>
+    <t>E_1_7_10</t>
+  </si>
+  <si>
+    <t>E_1_7_9</t>
+  </si>
+  <si>
+    <t>E_1_7_8</t>
+  </si>
+  <si>
+    <t>E_1_7_7</t>
+  </si>
+  <si>
+    <t>E_1_7_6</t>
+  </si>
+  <si>
+    <t>E_1_7_5</t>
+  </si>
+  <si>
+    <t>E_1_7_4</t>
+  </si>
+  <si>
+    <t>E_1_7_3</t>
+  </si>
+  <si>
+    <t>E_1_7_2</t>
+  </si>
+  <si>
+    <t>E_1_7_1</t>
+  </si>
+  <si>
+    <t>E_2_5_21</t>
+  </si>
+  <si>
+    <t>E_2_5_20</t>
+  </si>
+  <si>
+    <t>E_2_5_19</t>
+  </si>
+  <si>
+    <t>E_2_5_18</t>
+  </si>
+  <si>
+    <t>E_2_5_17</t>
+  </si>
+  <si>
+    <t>E_2_5_16</t>
+  </si>
+  <si>
+    <t>E_2_5_15</t>
+  </si>
+  <si>
+    <t>E_2_5_14</t>
+  </si>
+  <si>
+    <t>E_2_5_13</t>
+  </si>
+  <si>
+    <t>E_2_5_12</t>
+  </si>
+  <si>
+    <t>E_2_5_11</t>
+  </si>
+  <si>
+    <t>E_2_5_10</t>
+  </si>
+  <si>
+    <t>E_2_5_9</t>
+  </si>
+  <si>
+    <t>E_2_5_8</t>
+  </si>
+  <si>
+    <t>E_2_5_7</t>
+  </si>
+  <si>
+    <t>E_2_5_6</t>
+  </si>
+  <si>
+    <t>E_2_5_5</t>
+  </si>
+  <si>
+    <t>E_2_5_4</t>
+  </si>
+  <si>
+    <t>E_2_5_3</t>
+  </si>
+  <si>
+    <t>E_2_5_2</t>
+  </si>
+  <si>
+    <t>E_2_5_1</t>
+  </si>
+  <si>
+    <t>E_2_9_21</t>
+  </si>
+  <si>
+    <t>E_2_9_20</t>
+  </si>
+  <si>
+    <t>E_2_9_19</t>
+  </si>
+  <si>
+    <t>E_2_9_18</t>
+  </si>
+  <si>
+    <t>E_2_9_17</t>
+  </si>
+  <si>
+    <t>E_2_9_16</t>
+  </si>
+  <si>
+    <t>E_2_9_15</t>
+  </si>
+  <si>
+    <t>E_2_9_14</t>
+  </si>
+  <si>
+    <t>E_2_9_13</t>
+  </si>
+  <si>
+    <t>E_2_9_12</t>
+  </si>
+  <si>
+    <t>E_2_9_11</t>
+  </si>
+  <si>
+    <t>E_2_9_10</t>
+  </si>
+  <si>
+    <t>E_2_9_9</t>
+  </si>
+  <si>
+    <t>E_2_9_8</t>
+  </si>
+  <si>
+    <t>E_2_9_7</t>
+  </si>
+  <si>
+    <t>E_2_9_6</t>
+  </si>
+  <si>
+    <t>E_2_9_5</t>
+  </si>
+  <si>
+    <t>E_2_9_4</t>
+  </si>
+  <si>
+    <t>E_2_9_3</t>
+  </si>
+  <si>
+    <t>E_2_9_2</t>
+  </si>
+  <si>
+    <t>E_2_9_1</t>
+  </si>
+  <si>
+    <t>E_2_11_21</t>
+  </si>
+  <si>
+    <t>E_2_11_20</t>
+  </si>
+  <si>
+    <t>E_2_11_19</t>
+  </si>
+  <si>
+    <t>E_2_11_18</t>
+  </si>
+  <si>
+    <t>E_2_11_17</t>
+  </si>
+  <si>
+    <t>E_2_11_16</t>
+  </si>
+  <si>
+    <t>E_2_11_15</t>
+  </si>
+  <si>
+    <t>E_2_11_14</t>
+  </si>
+  <si>
+    <t>E_2_11_13</t>
+  </si>
+  <si>
+    <t>E_2_11_12</t>
+  </si>
+  <si>
+    <t>E_2_11_11</t>
+  </si>
+  <si>
+    <t>E_2_11_10</t>
+  </si>
+  <si>
+    <t>E_2_11_9</t>
+  </si>
+  <si>
+    <t>E_2_11_8</t>
+  </si>
+  <si>
+    <t>E_2_11_7</t>
+  </si>
+  <si>
+    <t>E_2_11_6</t>
+  </si>
+  <si>
+    <t>E_2_11_5</t>
+  </si>
+  <si>
+    <t>E_2_11_4</t>
+  </si>
+  <si>
+    <t>E_2_11_3</t>
+  </si>
+  <si>
+    <t>E_2_11_2</t>
+  </si>
+  <si>
+    <t>E_2_11_1</t>
+  </si>
+  <si>
+    <t>E_2_14_21</t>
+  </si>
+  <si>
+    <t>E_2_14_20</t>
+  </si>
+  <si>
+    <t>E_2_14_19</t>
+  </si>
+  <si>
+    <t>E_2_14_18</t>
+  </si>
+  <si>
+    <t>E_2_14_17</t>
+  </si>
+  <si>
+    <t>E_2_14_16</t>
+  </si>
+  <si>
+    <t>E_2_14_15</t>
+  </si>
+  <si>
+    <t>E_2_14_14</t>
+  </si>
+  <si>
+    <t>E_2_14_13</t>
+  </si>
+  <si>
+    <t>E_2_14_12</t>
+  </si>
+  <si>
+    <t>E_2_14_11</t>
+  </si>
+  <si>
+    <t>E_2_14_10</t>
+  </si>
+  <si>
+    <t>E_2_14_9</t>
+  </si>
+  <si>
+    <t>E_2_14_8</t>
+  </si>
+  <si>
+    <t>E_2_14_7</t>
+  </si>
+  <si>
+    <t>E_2_14_6</t>
+  </si>
+  <si>
+    <t>E_2_14_5</t>
+  </si>
+  <si>
+    <t>E_2_14_4</t>
+  </si>
+  <si>
+    <t>E_2_14_3</t>
+  </si>
+  <si>
+    <t>E_2_14_2</t>
+  </si>
+  <si>
+    <t>E_2_14_1</t>
+  </si>
+  <si>
+    <t>E_2_15_21</t>
+  </si>
+  <si>
+    <t>E_2_15_20</t>
+  </si>
+  <si>
+    <t>E_2_15_19</t>
+  </si>
+  <si>
+    <t>E_2_15_18</t>
+  </si>
+  <si>
+    <t>E_2_15_17</t>
+  </si>
+  <si>
+    <t>E_2_15_16</t>
+  </si>
+  <si>
+    <t>E_2_15_15</t>
+  </si>
+  <si>
+    <t>E_2_15_14</t>
+  </si>
+  <si>
+    <t>E_2_15_13</t>
+  </si>
+  <si>
+    <t>E_2_15_12</t>
+  </si>
+  <si>
+    <t>E_2_15_11</t>
+  </si>
+  <si>
+    <t>E_2_15_10</t>
+  </si>
+  <si>
+    <t>E_2_15_9</t>
+  </si>
+  <si>
+    <t>E_2_15_8</t>
+  </si>
+  <si>
+    <t>E_2_15_7</t>
+  </si>
+  <si>
+    <t>E_2_15_6</t>
+  </si>
+  <si>
+    <t>E_2_15_5</t>
+  </si>
+  <si>
+    <t>E_2_15_4</t>
+  </si>
+  <si>
+    <t>E_2_15_3</t>
+  </si>
+  <si>
+    <t>E_2_15_2</t>
+  </si>
+  <si>
+    <t>E_2_15_1</t>
+  </si>
+  <si>
+    <t>E_1_5_21</t>
+  </si>
+  <si>
+    <t>E_1_5_20</t>
+  </si>
+  <si>
+    <t>E_1_5_19</t>
+  </si>
+  <si>
+    <t>E_1_5_18</t>
+  </si>
+  <si>
+    <t>E_1_5_17</t>
+  </si>
+  <si>
+    <t>E_1_5_16</t>
+  </si>
+  <si>
+    <t>E_1_5_15</t>
+  </si>
+  <si>
+    <t>E_1_5_14</t>
+  </si>
+  <si>
+    <t>E_1_5_13</t>
+  </si>
+  <si>
+    <t>E_1_5_12</t>
+  </si>
+  <si>
+    <t>E_1_5_11</t>
+  </si>
+  <si>
+    <t>E_1_5_10</t>
+  </si>
+  <si>
+    <t>E_1_5_9</t>
+  </si>
+  <si>
+    <t>E_1_5_8</t>
+  </si>
+  <si>
+    <t>E_1_5_7</t>
+  </si>
+  <si>
+    <t>E_1_5_6</t>
+  </si>
+  <si>
+    <t>E_1_5_5</t>
+  </si>
+  <si>
+    <t>E_1_5_4</t>
+  </si>
+  <si>
+    <t>E_1_5_3</t>
+  </si>
+  <si>
+    <t>E_1_5_2</t>
+  </si>
+  <si>
+    <t>E_1_5_1</t>
+  </si>
+  <si>
+    <t>E_1_4_21</t>
+  </si>
+  <si>
+    <t>E_1_4_20</t>
+  </si>
+  <si>
+    <t>E_1_4_19</t>
+  </si>
+  <si>
+    <t>E_1_4_18</t>
+  </si>
+  <si>
+    <t>E_1_4_17</t>
+  </si>
+  <si>
+    <t>E_1_4_16</t>
+  </si>
+  <si>
+    <t>E_1_4_15</t>
+  </si>
+  <si>
+    <t>E_1_4_14</t>
+  </si>
+  <si>
+    <t>E_1_4_13</t>
+  </si>
+  <si>
+    <t>E_1_4_12</t>
+  </si>
+  <si>
+    <t>E_1_4_11</t>
+  </si>
+  <si>
+    <t>E_1_4_10</t>
+  </si>
+  <si>
+    <t>E_1_4_9</t>
+  </si>
+  <si>
+    <t>E_1_4_8</t>
+  </si>
+  <si>
+    <t>E_1_4_7</t>
+  </si>
+  <si>
+    <t>E_1_4_6</t>
+  </si>
+  <si>
+    <t>E_1_4_5</t>
+  </si>
+  <si>
+    <t>E_1_4_4</t>
+  </si>
+  <si>
+    <t>E_1_4_3</t>
+  </si>
+  <si>
+    <t>E_1_4_2</t>
+  </si>
+  <si>
+    <t>E_1_4_1</t>
+  </si>
+  <si>
+    <t>E_1_3_21</t>
+  </si>
+  <si>
+    <t>E_1_3_20</t>
+  </si>
+  <si>
+    <t>E_1_3_19</t>
+  </si>
+  <si>
+    <t>E_1_3_18</t>
+  </si>
+  <si>
+    <t>E_1_3_17</t>
+  </si>
+  <si>
+    <t>E_1_3_16</t>
+  </si>
+  <si>
+    <t>E_1_3_15</t>
+  </si>
+  <si>
+    <t>E_1_3_14</t>
+  </si>
+  <si>
+    <t>E_1_3_13</t>
+  </si>
+  <si>
+    <t>E_1_3_12</t>
+  </si>
+  <si>
+    <t>E_1_3_11</t>
+  </si>
+  <si>
+    <t>E_1_3_10</t>
+  </si>
+  <si>
+    <t>E_1_3_9</t>
+  </si>
+  <si>
+    <t>E_1_3_8</t>
+  </si>
+  <si>
+    <t>E_1_3_7</t>
+  </si>
+  <si>
+    <t>E_1_3_6</t>
+  </si>
+  <si>
+    <t>E_1_3_5</t>
+  </si>
+  <si>
+    <t>E_1_3_4</t>
+  </si>
+  <si>
+    <t>E_1_3_3</t>
+  </si>
+  <si>
+    <t>E_1_3_2</t>
+  </si>
+  <si>
+    <t>E_1_3_1</t>
+  </si>
+  <si>
+    <t>E_1_1_21</t>
+  </si>
+  <si>
+    <t>E_1_1_20</t>
+  </si>
+  <si>
+    <t>E_1_1_19</t>
+  </si>
+  <si>
+    <t>E_1_1_18</t>
+  </si>
+  <si>
+    <t>E_1_1_17</t>
+  </si>
+  <si>
+    <t>E_1_1_16</t>
+  </si>
+  <si>
+    <t>E_1_1_15</t>
+  </si>
+  <si>
+    <t>E_1_1_14</t>
+  </si>
+  <si>
+    <t>E_1_1_13</t>
+  </si>
+  <si>
+    <t>E_1_1_12</t>
+  </si>
+  <si>
+    <t>E_1_1_11</t>
+  </si>
+  <si>
+    <t>E_1_1_10</t>
+  </si>
+  <si>
+    <t>E_1_1_9</t>
+  </si>
+  <si>
+    <t>E_1_1_8</t>
+  </si>
+  <si>
+    <t>E_1_1_7</t>
+  </si>
+  <si>
+    <t>E_1_1_6</t>
+  </si>
+  <si>
+    <t>E_1_1_5</t>
+  </si>
+  <si>
+    <t>E_1_1_4</t>
+  </si>
+  <si>
+    <t>E_1_1_3</t>
+  </si>
+  <si>
+    <t>E_1_1_2</t>
+  </si>
+  <si>
+    <t>E_1_1_1</t>
+  </si>
+  <si>
+    <t>E_2_4_21</t>
+  </si>
+  <si>
+    <t>E_2_4_20</t>
+  </si>
+  <si>
+    <t>E_2_4_19</t>
+  </si>
+  <si>
+    <t>E_2_4_18</t>
+  </si>
+  <si>
+    <t>E_2_4_17</t>
+  </si>
+  <si>
+    <t>E_2_4_16</t>
+  </si>
+  <si>
+    <t>E_2_4_15</t>
+  </si>
+  <si>
+    <t>E_2_4_14</t>
+  </si>
+  <si>
+    <t>E_2_4_13</t>
+  </si>
+  <si>
+    <t>E_2_4_12</t>
+  </si>
+  <si>
+    <t>E_2_4_11</t>
+  </si>
+  <si>
+    <t>E_2_4_10</t>
+  </si>
+  <si>
+    <t>E_2_4_9</t>
+  </si>
+  <si>
+    <t>E_2_4_8</t>
+  </si>
+  <si>
+    <t>E_2_4_7</t>
+  </si>
+  <si>
+    <t>E_2_4_6</t>
+  </si>
+  <si>
+    <t>E_2_4_5</t>
+  </si>
+  <si>
+    <t>E_2_4_4</t>
+  </si>
+  <si>
+    <t>E_2_4_3</t>
+  </si>
+  <si>
+    <t>E_2_4_2</t>
+  </si>
+  <si>
+    <t>E_2_4_1</t>
+  </si>
+  <si>
+    <t>E_2_3_21</t>
+  </si>
+  <si>
+    <t>E_2_3_20</t>
+  </si>
+  <si>
+    <t>E_2_3_19</t>
+  </si>
+  <si>
+    <t>E_2_3_18</t>
+  </si>
+  <si>
+    <t>E_2_3_17</t>
+  </si>
+  <si>
+    <t>E_2_3_16</t>
+  </si>
+  <si>
+    <t>E_2_3_15</t>
+  </si>
+  <si>
+    <t>E_2_3_14</t>
+  </si>
+  <si>
+    <t>E_2_3_13</t>
+  </si>
+  <si>
+    <t>E_2_3_12</t>
+  </si>
+  <si>
+    <t>E_2_3_11</t>
+  </si>
+  <si>
+    <t>E_2_3_10</t>
+  </si>
+  <si>
+    <t>E_2_3_9</t>
+  </si>
+  <si>
+    <t>E_2_3_8</t>
+  </si>
+  <si>
+    <t>E_2_3_7</t>
+  </si>
+  <si>
+    <t>E_2_3_6</t>
+  </si>
+  <si>
+    <t>E_2_3_5</t>
+  </si>
+  <si>
+    <t>E_2_3_4</t>
+  </si>
+  <si>
+    <t>E_2_3_3</t>
+  </si>
+  <si>
+    <t>E_2_3_2</t>
+  </si>
+  <si>
+    <t>E_2_3_1</t>
+  </si>
+  <si>
+    <t>E_2_1_21</t>
+  </si>
+  <si>
+    <t>E_2_1_20</t>
+  </si>
+  <si>
+    <t>E_2_1_19</t>
+  </si>
+  <si>
+    <t>E_2_1_18</t>
+  </si>
+  <si>
+    <t>E_2_1_17</t>
+  </si>
+  <si>
+    <t>E_2_1_16</t>
+  </si>
+  <si>
+    <t>E_2_1_15</t>
+  </si>
+  <si>
+    <t>E_2_1_14</t>
+  </si>
+  <si>
+    <t>E_2_1_13</t>
+  </si>
+  <si>
+    <t>E_2_1_12</t>
+  </si>
+  <si>
+    <t>E_2_1_11</t>
+  </si>
+  <si>
+    <t>E_2_1_10</t>
+  </si>
+  <si>
+    <t>E_2_1_9</t>
+  </si>
+  <si>
+    <t>E_2_1_8</t>
+  </si>
+  <si>
+    <t>E_2_1_7</t>
+  </si>
+  <si>
+    <t>E_2_1_6</t>
+  </si>
+  <si>
+    <t>E_2_1_5</t>
+  </si>
+  <si>
+    <t>E_2_1_4</t>
+  </si>
+  <si>
+    <t>E_2_1_3</t>
+  </si>
+  <si>
+    <t>E_2_1_2</t>
+  </si>
+  <si>
+    <t>E_2_1_1</t>
+  </si>
+  <si>
+    <t>E_2_8_21</t>
+  </si>
+  <si>
+    <t>E_2_8_20</t>
+  </si>
+  <si>
+    <t>E_2_8_19</t>
+  </si>
+  <si>
+    <t>E_2_8_18</t>
+  </si>
+  <si>
+    <t>E_2_8_17</t>
+  </si>
+  <si>
+    <t>E_2_8_16</t>
+  </si>
+  <si>
+    <t>E_2_8_15</t>
+  </si>
+  <si>
+    <t>E_2_8_14</t>
+  </si>
+  <si>
+    <t>E_2_8_13</t>
+  </si>
+  <si>
+    <t>E_2_8_12</t>
+  </si>
+  <si>
+    <t>E_2_8_11</t>
+  </si>
+  <si>
+    <t>E_2_8_10</t>
+  </si>
+  <si>
+    <t>E_2_8_9</t>
+  </si>
+  <si>
+    <t>E_2_8_8</t>
+  </si>
+  <si>
+    <t>E_2_8_7</t>
+  </si>
+  <si>
+    <t>E_2_8_6</t>
+  </si>
+  <si>
+    <t>E_2_8_5</t>
+  </si>
+  <si>
+    <t>E_2_8_4</t>
+  </si>
+  <si>
+    <t>E_2_8_3</t>
+  </si>
+  <si>
+    <t>E_2_8_2</t>
+  </si>
+  <si>
+    <t>E_2_8_1</t>
+  </si>
+  <si>
+    <t>E_2_6_21</t>
+  </si>
+  <si>
+    <t>E_2_6_20</t>
+  </si>
+  <si>
+    <t>E_2_6_19</t>
+  </si>
+  <si>
+    <t>E_2_6_18</t>
+  </si>
+  <si>
+    <t>E_2_6_17</t>
+  </si>
+  <si>
+    <t>E_2_6_16</t>
+  </si>
+  <si>
+    <t>E_2_6_15</t>
+  </si>
+  <si>
+    <t>E_2_6_14</t>
+  </si>
+  <si>
+    <t>E_2_6_13</t>
+  </si>
+  <si>
+    <t>E_2_6_12</t>
+  </si>
+  <si>
+    <t>E_2_6_11</t>
+  </si>
+  <si>
+    <t>E_2_6_10</t>
+  </si>
+  <si>
+    <t>E_2_6_9</t>
+  </si>
+  <si>
+    <t>E_2_6_8</t>
+  </si>
+  <si>
+    <t>E_2_6_7</t>
+  </si>
+  <si>
+    <t>E_2_6_6</t>
+  </si>
+  <si>
+    <t>E_2_6_5</t>
+  </si>
+  <si>
+    <t>E_2_6_4</t>
+  </si>
+  <si>
+    <t>E_2_6_3</t>
+  </si>
+  <si>
+    <t>E_2_6_2</t>
+  </si>
+  <si>
+    <t>E_2_6_1</t>
+  </si>
+  <si>
+    <t>E_2_2_21</t>
+  </si>
+  <si>
+    <t>E_2_2_20</t>
+  </si>
+  <si>
+    <t>E_2_2_19</t>
+  </si>
+  <si>
+    <t>E_2_2_18</t>
+  </si>
+  <si>
+    <t>E_2_2_17</t>
+  </si>
+  <si>
+    <t>E_2_2_16</t>
+  </si>
+  <si>
+    <t>E_2_2_15</t>
+  </si>
+  <si>
+    <t>E_2_2_14</t>
+  </si>
+  <si>
+    <t>E_2_2_13</t>
+  </si>
+  <si>
+    <t>E_2_2_12</t>
+  </si>
+  <si>
+    <t>E_2_2_11</t>
+  </si>
+  <si>
+    <t>E_2_2_10</t>
+  </si>
+  <si>
+    <t>E_2_2_9</t>
+  </si>
+  <si>
+    <t>E_2_2_8</t>
+  </si>
+  <si>
+    <t>E_2_2_7</t>
+  </si>
+  <si>
+    <t>E_2_2_6</t>
+  </si>
+  <si>
+    <t>E_2_2_5</t>
+  </si>
+  <si>
+    <t>E_2_2_4</t>
+  </si>
+  <si>
+    <t>E_2_2_3</t>
+  </si>
+  <si>
+    <t>E_2_2_2</t>
+  </si>
+  <si>
+    <t>E_2_2_1</t>
   </si>
 </sst>
 </file>
@@ -2567,7 +3575,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37F45055-F8B8-9843-8A9F-BDE4FA1E6DAC}">
-  <dimension ref="A1:D715"/>
+  <dimension ref="A1:D1051"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -12585,6 +13593,4710 @@
         <v>13.355420000000001</v>
       </c>
     </row>
+    <row r="716" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A716" t="s">
+        <v>718</v>
+      </c>
+      <c r="B716">
+        <v>12.817679999999999</v>
+      </c>
+      <c r="C716">
+        <v>1.7867200000000001</v>
+      </c>
+      <c r="D716">
+        <v>13.578709999999999</v>
+      </c>
+    </row>
+    <row r="717" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A717" t="s">
+        <v>719</v>
+      </c>
+      <c r="B717">
+        <v>12.89823</v>
+      </c>
+      <c r="C717">
+        <v>1.8730100000000001</v>
+      </c>
+      <c r="D717">
+        <v>13.577909999999999</v>
+      </c>
+    </row>
+    <row r="718" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A718" t="s">
+        <v>720</v>
+      </c>
+      <c r="B718">
+        <v>12.79677</v>
+      </c>
+      <c r="C718">
+        <v>1.9756400000000001</v>
+      </c>
+      <c r="D718">
+        <v>13.48747</v>
+      </c>
+    </row>
+    <row r="719" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A719" t="s">
+        <v>721</v>
+      </c>
+      <c r="B719">
+        <v>12.69638</v>
+      </c>
+      <c r="C719">
+        <v>1.9042300000000001</v>
+      </c>
+      <c r="D719">
+        <v>13.36093</v>
+      </c>
+    </row>
+    <row r="720" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A720" t="s">
+        <v>722</v>
+      </c>
+      <c r="B720">
+        <v>12.881399999999999</v>
+      </c>
+      <c r="C720">
+        <v>1.8363499999999999</v>
+      </c>
+      <c r="D720">
+        <v>13.470560000000001</v>
+      </c>
+    </row>
+    <row r="721" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A721" t="s">
+        <v>723</v>
+      </c>
+      <c r="B721">
+        <v>12.842219999999999</v>
+      </c>
+      <c r="C721">
+        <v>1.7883</v>
+      </c>
+      <c r="D721">
+        <v>13.39259</v>
+      </c>
+    </row>
+    <row r="722" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A722" t="s">
+        <v>724</v>
+      </c>
+      <c r="B722">
+        <v>12.931290000000001</v>
+      </c>
+      <c r="C722">
+        <v>1.97248</v>
+      </c>
+      <c r="D722">
+        <v>13.5101</v>
+      </c>
+    </row>
+    <row r="723" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A723" t="s">
+        <v>725</v>
+      </c>
+      <c r="B723">
+        <v>12.859170000000001</v>
+      </c>
+      <c r="C723">
+        <v>1.98472</v>
+      </c>
+      <c r="D723">
+        <v>13.43817</v>
+      </c>
+    </row>
+    <row r="724" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A724" t="s">
+        <v>726</v>
+      </c>
+      <c r="B724">
+        <v>12.840310000000001</v>
+      </c>
+      <c r="C724">
+        <v>1.72072</v>
+      </c>
+      <c r="D724">
+        <v>13.34329</v>
+      </c>
+    </row>
+    <row r="725" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A725" t="s">
+        <v>727</v>
+      </c>
+      <c r="B725">
+        <v>12.8081</v>
+      </c>
+      <c r="C725">
+        <v>1.6949000000000001</v>
+      </c>
+      <c r="D725">
+        <v>13.272729999999999</v>
+      </c>
+    </row>
+    <row r="726" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A726" t="s">
+        <v>728</v>
+      </c>
+      <c r="B726">
+        <v>12.795260000000001</v>
+      </c>
+      <c r="C726">
+        <v>1.8222799999999999</v>
+      </c>
+      <c r="D726">
+        <v>13.218999999999999</v>
+      </c>
+    </row>
+    <row r="727" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A727" t="s">
+        <v>729</v>
+      </c>
+      <c r="B727">
+        <v>12.76797</v>
+      </c>
+      <c r="C727">
+        <v>1.97289</v>
+      </c>
+      <c r="D727">
+        <v>13.204879999999999</v>
+      </c>
+    </row>
+    <row r="728" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A728" t="s">
+        <v>730</v>
+      </c>
+      <c r="B728">
+        <v>12.83487</v>
+      </c>
+      <c r="C728">
+        <v>1.90832</v>
+      </c>
+      <c r="D728">
+        <v>13.23152</v>
+      </c>
+    </row>
+    <row r="729" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A729" t="s">
+        <v>731</v>
+      </c>
+      <c r="B729">
+        <v>12.738569999999999</v>
+      </c>
+      <c r="C729">
+        <v>1.9579599999999999</v>
+      </c>
+      <c r="D729">
+        <v>13.136649999999999</v>
+      </c>
+    </row>
+    <row r="730" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A730" t="s">
+        <v>732</v>
+      </c>
+      <c r="B730">
+        <v>12.68885</v>
+      </c>
+      <c r="C730">
+        <v>1.6407099999999999</v>
+      </c>
+      <c r="D730">
+        <v>13.01047</v>
+      </c>
+    </row>
+    <row r="731" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A731" t="s">
+        <v>733</v>
+      </c>
+      <c r="B731">
+        <v>12.966530000000001</v>
+      </c>
+      <c r="C731">
+        <v>1.7291799999999999</v>
+      </c>
+      <c r="D731">
+        <v>13.279450000000001</v>
+      </c>
+    </row>
+    <row r="732" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A732" t="s">
+        <v>734</v>
+      </c>
+      <c r="B732">
+        <v>12.80095</v>
+      </c>
+      <c r="C732">
+        <v>1.65157</v>
+      </c>
+      <c r="D732">
+        <v>13.08488</v>
+      </c>
+    </row>
+    <row r="733" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A733" t="s">
+        <v>735</v>
+      </c>
+      <c r="B733">
+        <v>12.80817</v>
+      </c>
+      <c r="C733">
+        <v>1.96837</v>
+      </c>
+      <c r="D733">
+        <v>13.158250000000001</v>
+      </c>
+    </row>
+    <row r="734" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A734" t="s">
+        <v>736</v>
+      </c>
+      <c r="B734">
+        <v>12.828939999999999</v>
+      </c>
+      <c r="C734">
+        <v>1.84711</v>
+      </c>
+      <c r="D734">
+        <v>13.23118</v>
+      </c>
+    </row>
+    <row r="735" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A735" t="s">
+        <v>737</v>
+      </c>
+      <c r="B735">
+        <v>12.8066</v>
+      </c>
+      <c r="C735">
+        <v>1.9658199999999999</v>
+      </c>
+      <c r="D735">
+        <v>13.25488</v>
+      </c>
+    </row>
+    <row r="736" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A736" t="s">
+        <v>738</v>
+      </c>
+      <c r="B736">
+        <v>12.873239999999999</v>
+      </c>
+      <c r="C736">
+        <v>1.81959</v>
+      </c>
+      <c r="D736">
+        <v>13.216100000000001</v>
+      </c>
+    </row>
+    <row r="737" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A737" t="s">
+        <v>739</v>
+      </c>
+      <c r="B737">
+        <v>12.71214</v>
+      </c>
+      <c r="C737">
+        <v>1.89062</v>
+      </c>
+      <c r="D737">
+        <v>13.521559999999999</v>
+      </c>
+    </row>
+    <row r="738" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A738" t="s">
+        <v>740</v>
+      </c>
+      <c r="B738">
+        <v>12.848380000000001</v>
+      </c>
+      <c r="C738">
+        <v>1.87168</v>
+      </c>
+      <c r="D738">
+        <v>13.653930000000001</v>
+      </c>
+    </row>
+    <row r="739" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A739" t="s">
+        <v>741</v>
+      </c>
+      <c r="B739">
+        <v>12.83846</v>
+      </c>
+      <c r="C739">
+        <v>1.8405800000000001</v>
+      </c>
+      <c r="D739">
+        <v>13.62106</v>
+      </c>
+    </row>
+    <row r="740" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A740" t="s">
+        <v>742</v>
+      </c>
+      <c r="B740">
+        <v>12.728569999999999</v>
+      </c>
+      <c r="C740">
+        <v>1.9075299999999999</v>
+      </c>
+      <c r="D740">
+        <v>13.54846</v>
+      </c>
+    </row>
+    <row r="741" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A741" t="s">
+        <v>743</v>
+      </c>
+      <c r="B741">
+        <v>12.823320000000001</v>
+      </c>
+      <c r="C741">
+        <v>1.9487099999999999</v>
+      </c>
+      <c r="D741">
+        <v>13.65474</v>
+      </c>
+    </row>
+    <row r="742" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A742" t="s">
+        <v>744</v>
+      </c>
+      <c r="B742">
+        <v>12.79096</v>
+      </c>
+      <c r="C742">
+        <v>1.93814</v>
+      </c>
+      <c r="D742">
+        <v>13.631349999999999</v>
+      </c>
+    </row>
+    <row r="743" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A743" t="s">
+        <v>745</v>
+      </c>
+      <c r="B743">
+        <v>12.72282</v>
+      </c>
+      <c r="C743">
+        <v>1.8250599999999999</v>
+      </c>
+      <c r="D743">
+        <v>13.532120000000001</v>
+      </c>
+    </row>
+    <row r="744" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A744" t="s">
+        <v>746</v>
+      </c>
+      <c r="B744">
+        <v>12.690939999999999</v>
+      </c>
+      <c r="C744">
+        <v>1.8706799999999999</v>
+      </c>
+      <c r="D744">
+        <v>13.545489999999999</v>
+      </c>
+    </row>
+    <row r="745" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A745" t="s">
+        <v>747</v>
+      </c>
+      <c r="B745">
+        <v>12.841419999999999</v>
+      </c>
+      <c r="C745">
+        <v>1.91184</v>
+      </c>
+      <c r="D745">
+        <v>13.75845</v>
+      </c>
+    </row>
+    <row r="746" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A746" t="s">
+        <v>748</v>
+      </c>
+      <c r="B746">
+        <v>12.84571</v>
+      </c>
+      <c r="C746">
+        <v>1.97119</v>
+      </c>
+      <c r="D746">
+        <v>13.79833</v>
+      </c>
+    </row>
+    <row r="747" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A747" t="s">
+        <v>749</v>
+      </c>
+      <c r="B747">
+        <v>12.810029999999999</v>
+      </c>
+      <c r="C747">
+        <v>1.87836</v>
+      </c>
+      <c r="D747">
+        <v>13.718159999999999</v>
+      </c>
+    </row>
+    <row r="748" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A748" t="s">
+        <v>750</v>
+      </c>
+      <c r="B748">
+        <v>12.87172</v>
+      </c>
+      <c r="C748">
+        <v>1.8779699999999999</v>
+      </c>
+      <c r="D748">
+        <v>13.77234</v>
+      </c>
+    </row>
+    <row r="749" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A749" t="s">
+        <v>751</v>
+      </c>
+      <c r="B749">
+        <v>12.89658</v>
+      </c>
+      <c r="C749">
+        <v>1.8476399999999999</v>
+      </c>
+      <c r="D749">
+        <v>13.776109999999999</v>
+      </c>
+    </row>
+    <row r="750" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A750" t="s">
+        <v>752</v>
+      </c>
+      <c r="B750">
+        <v>12.860290000000001</v>
+      </c>
+      <c r="C750">
+        <v>1.9933000000000001</v>
+      </c>
+      <c r="D750">
+        <v>13.765930000000001</v>
+      </c>
+    </row>
+    <row r="751" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A751" t="s">
+        <v>753</v>
+      </c>
+      <c r="B751">
+        <v>12.76286</v>
+      </c>
+      <c r="C751">
+        <v>1.8406</v>
+      </c>
+      <c r="D751">
+        <v>13.611280000000001</v>
+      </c>
+    </row>
+    <row r="752" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A752" t="s">
+        <v>754</v>
+      </c>
+      <c r="B752">
+        <v>12.81133</v>
+      </c>
+      <c r="C752">
+        <v>1.94156</v>
+      </c>
+      <c r="D752">
+        <v>13.67103</v>
+      </c>
+    </row>
+    <row r="753" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A753" t="s">
+        <v>755</v>
+      </c>
+      <c r="B753">
+        <v>12.762309999999999</v>
+      </c>
+      <c r="C753">
+        <v>1.93055</v>
+      </c>
+      <c r="D753">
+        <v>13.450329999999999</v>
+      </c>
+    </row>
+    <row r="754" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A754" t="s">
+        <v>756</v>
+      </c>
+      <c r="B754">
+        <v>12.80123</v>
+      </c>
+      <c r="C754">
+        <v>1.78867</v>
+      </c>
+      <c r="D754">
+        <v>13.430400000000001</v>
+      </c>
+    </row>
+    <row r="755" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A755" t="s">
+        <v>757</v>
+      </c>
+      <c r="B755">
+        <v>12.83385</v>
+      </c>
+      <c r="C755">
+        <v>1.8908499999999999</v>
+      </c>
+      <c r="D755">
+        <v>13.573969999999999</v>
+      </c>
+    </row>
+    <row r="756" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A756" t="s">
+        <v>758</v>
+      </c>
+      <c r="B756">
+        <v>12.89804</v>
+      </c>
+      <c r="C756">
+        <v>1.9490099999999999</v>
+      </c>
+      <c r="D756">
+        <v>13.69538</v>
+      </c>
+    </row>
+    <row r="757" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A757" t="s">
+        <v>759</v>
+      </c>
+      <c r="B757">
+        <v>12.85534</v>
+      </c>
+      <c r="C757">
+        <v>1.9601999999999999</v>
+      </c>
+      <c r="D757">
+        <v>13.630459999999999</v>
+      </c>
+    </row>
+    <row r="758" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A758" t="s">
+        <v>760</v>
+      </c>
+      <c r="B758">
+        <v>12.78777</v>
+      </c>
+      <c r="C758">
+        <v>1.9039699999999999</v>
+      </c>
+      <c r="D758">
+        <v>13.47589</v>
+      </c>
+    </row>
+    <row r="759" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A759" t="s">
+        <v>761</v>
+      </c>
+      <c r="B759">
+        <v>12.92384</v>
+      </c>
+      <c r="C759">
+        <v>1.93916</v>
+      </c>
+      <c r="D759">
+        <v>13.664009999999999</v>
+      </c>
+    </row>
+    <row r="760" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A760" t="s">
+        <v>762</v>
+      </c>
+      <c r="B760">
+        <v>12.82818</v>
+      </c>
+      <c r="C760">
+        <v>1.89974</v>
+      </c>
+      <c r="D760">
+        <v>13.551119999999999</v>
+      </c>
+    </row>
+    <row r="761" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A761" t="s">
+        <v>763</v>
+      </c>
+      <c r="B761">
+        <v>12.78246</v>
+      </c>
+      <c r="C761">
+        <v>1.9958800000000001</v>
+      </c>
+      <c r="D761">
+        <v>13.58469</v>
+      </c>
+    </row>
+    <row r="762" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A762" t="s">
+        <v>764</v>
+      </c>
+      <c r="B762">
+        <v>12.7408</v>
+      </c>
+      <c r="C762">
+        <v>1.8314900000000001</v>
+      </c>
+      <c r="D762">
+        <v>13.51266</v>
+      </c>
+    </row>
+    <row r="763" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A763" t="s">
+        <v>765</v>
+      </c>
+      <c r="B763">
+        <v>12.97911</v>
+      </c>
+      <c r="C763">
+        <v>1.97305</v>
+      </c>
+      <c r="D763">
+        <v>13.829359999999999</v>
+      </c>
+    </row>
+    <row r="764" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A764" t="s">
+        <v>766</v>
+      </c>
+      <c r="B764">
+        <v>12.881629999999999</v>
+      </c>
+      <c r="C764">
+        <v>1.9830399999999999</v>
+      </c>
+      <c r="D764">
+        <v>13.74855</v>
+      </c>
+    </row>
+    <row r="765" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A765" t="s">
+        <v>767</v>
+      </c>
+      <c r="B765">
+        <v>12.86961</v>
+      </c>
+      <c r="C765">
+        <v>1.8981300000000001</v>
+      </c>
+      <c r="D765">
+        <v>13.713760000000001</v>
+      </c>
+    </row>
+    <row r="766" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A766" t="s">
+        <v>768</v>
+      </c>
+      <c r="B766">
+        <v>12.814640000000001</v>
+      </c>
+      <c r="C766">
+        <v>1.96977</v>
+      </c>
+      <c r="D766">
+        <v>13.696870000000001</v>
+      </c>
+    </row>
+    <row r="767" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A767" t="s">
+        <v>769</v>
+      </c>
+      <c r="B767">
+        <v>12.84118</v>
+      </c>
+      <c r="C767">
+        <v>1.9373</v>
+      </c>
+      <c r="D767">
+        <v>13.687580000000001</v>
+      </c>
+    </row>
+    <row r="768" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A768" t="s">
+        <v>770</v>
+      </c>
+      <c r="B768">
+        <v>12.737869999999999</v>
+      </c>
+      <c r="C768">
+        <v>1.96078</v>
+      </c>
+      <c r="D768">
+        <v>13.61909</v>
+      </c>
+    </row>
+    <row r="769" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A769" t="s">
+        <v>771</v>
+      </c>
+      <c r="B769">
+        <v>12.8462</v>
+      </c>
+      <c r="C769">
+        <v>1.8404499999999999</v>
+      </c>
+      <c r="D769">
+        <v>13.688829999999999</v>
+      </c>
+    </row>
+    <row r="770" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A770" t="s">
+        <v>772</v>
+      </c>
+      <c r="B770">
+        <v>12.833970000000001</v>
+      </c>
+      <c r="C770">
+        <v>1.9554199999999999</v>
+      </c>
+      <c r="D770">
+        <v>13.71927</v>
+      </c>
+    </row>
+    <row r="771" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A771" t="s">
+        <v>773</v>
+      </c>
+      <c r="B771">
+        <v>12.84703</v>
+      </c>
+      <c r="C771">
+        <v>1.9545600000000001</v>
+      </c>
+      <c r="D771">
+        <v>13.735580000000001</v>
+      </c>
+    </row>
+    <row r="772" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A772" t="s">
+        <v>774</v>
+      </c>
+      <c r="B772">
+        <v>12.82577</v>
+      </c>
+      <c r="C772">
+        <v>1.86436</v>
+      </c>
+      <c r="D772">
+        <v>13.678089999999999</v>
+      </c>
+    </row>
+    <row r="773" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A773" t="s">
+        <v>775</v>
+      </c>
+      <c r="B773">
+        <v>12.82943</v>
+      </c>
+      <c r="C773">
+        <v>1.9262600000000001</v>
+      </c>
+      <c r="D773">
+        <v>13.681839999999999</v>
+      </c>
+    </row>
+    <row r="774" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A774" t="s">
+        <v>776</v>
+      </c>
+      <c r="B774">
+        <v>12.96062</v>
+      </c>
+      <c r="C774">
+        <v>1.8916999999999999</v>
+      </c>
+      <c r="D774">
+        <v>13.751670000000001</v>
+      </c>
+    </row>
+    <row r="775" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A775" t="s">
+        <v>777</v>
+      </c>
+      <c r="B775">
+        <v>12.88317</v>
+      </c>
+      <c r="C775">
+        <v>1.8899600000000001</v>
+      </c>
+      <c r="D775">
+        <v>13.60313</v>
+      </c>
+    </row>
+    <row r="776" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A776" t="s">
+        <v>778</v>
+      </c>
+      <c r="B776">
+        <v>12.863530000000001</v>
+      </c>
+      <c r="C776">
+        <v>1.8507100000000001</v>
+      </c>
+      <c r="D776">
+        <v>13.5715</v>
+      </c>
+    </row>
+    <row r="777" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A777" t="s">
+        <v>779</v>
+      </c>
+      <c r="B777">
+        <v>12.690189999999999</v>
+      </c>
+      <c r="C777">
+        <v>1.9385300000000001</v>
+      </c>
+      <c r="D777">
+        <v>13.40366</v>
+      </c>
+    </row>
+    <row r="778" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A778" t="s">
+        <v>780</v>
+      </c>
+      <c r="B778">
+        <v>12.74489</v>
+      </c>
+      <c r="C778">
+        <v>1.98668</v>
+      </c>
+      <c r="D778">
+        <v>13.441330000000001</v>
+      </c>
+    </row>
+    <row r="779" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A779" t="s">
+        <v>781</v>
+      </c>
+      <c r="B779">
+        <v>12.768079999999999</v>
+      </c>
+      <c r="C779">
+        <v>1.93483</v>
+      </c>
+      <c r="D779">
+        <v>13.32551</v>
+      </c>
+    </row>
+    <row r="780" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A780" t="s">
+        <v>782</v>
+      </c>
+      <c r="B780">
+        <v>12.852220000000001</v>
+      </c>
+      <c r="C780">
+        <v>1.94469</v>
+      </c>
+      <c r="D780">
+        <v>13.37407</v>
+      </c>
+    </row>
+    <row r="781" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A781" t="s">
+        <v>783</v>
+      </c>
+      <c r="B781">
+        <v>12.758789999999999</v>
+      </c>
+      <c r="C781">
+        <v>1.9268799999999999</v>
+      </c>
+      <c r="D781">
+        <v>13.29669</v>
+      </c>
+    </row>
+    <row r="782" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A782" t="s">
+        <v>784</v>
+      </c>
+      <c r="B782">
+        <v>12.793430000000001</v>
+      </c>
+      <c r="C782">
+        <v>1.8700399999999999</v>
+      </c>
+      <c r="D782">
+        <v>13.34366</v>
+      </c>
+    </row>
+    <row r="783" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A783" t="s">
+        <v>785</v>
+      </c>
+      <c r="B783">
+        <v>12.73603</v>
+      </c>
+      <c r="C783">
+        <v>1.8729800000000001</v>
+      </c>
+      <c r="D783">
+        <v>13.314690000000001</v>
+      </c>
+    </row>
+    <row r="784" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A784" t="s">
+        <v>786</v>
+      </c>
+      <c r="B784">
+        <v>12.863490000000001</v>
+      </c>
+      <c r="C784">
+        <v>1.9691099999999999</v>
+      </c>
+      <c r="D784">
+        <v>13.471069999999999</v>
+      </c>
+    </row>
+    <row r="785" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A785" t="s">
+        <v>787</v>
+      </c>
+      <c r="B785">
+        <v>12.820180000000001</v>
+      </c>
+      <c r="C785">
+        <v>1.91357</v>
+      </c>
+      <c r="D785">
+        <v>13.42962</v>
+      </c>
+    </row>
+    <row r="786" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A786" t="s">
+        <v>788</v>
+      </c>
+      <c r="B786">
+        <v>12.6532</v>
+      </c>
+      <c r="C786">
+        <v>1.8073900000000001</v>
+      </c>
+      <c r="D786">
+        <v>13.237259999999999</v>
+      </c>
+    </row>
+    <row r="787" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A787" t="s">
+        <v>789</v>
+      </c>
+      <c r="B787">
+        <v>12.797739999999999</v>
+      </c>
+      <c r="C787">
+        <v>1.95173</v>
+      </c>
+      <c r="D787">
+        <v>13.429919999999999</v>
+      </c>
+    </row>
+    <row r="788" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A788" t="s">
+        <v>790</v>
+      </c>
+      <c r="B788">
+        <v>12.79888</v>
+      </c>
+      <c r="C788">
+        <v>1.9744900000000001</v>
+      </c>
+      <c r="D788">
+        <v>13.473050000000001</v>
+      </c>
+    </row>
+    <row r="789" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A789" t="s">
+        <v>791</v>
+      </c>
+      <c r="B789">
+        <v>12.78426</v>
+      </c>
+      <c r="C789">
+        <v>1.9085399999999999</v>
+      </c>
+      <c r="D789">
+        <v>13.462289999999999</v>
+      </c>
+    </row>
+    <row r="790" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A790" t="s">
+        <v>792</v>
+      </c>
+      <c r="B790">
+        <v>12.892609999999999</v>
+      </c>
+      <c r="C790">
+        <v>1.9791799999999999</v>
+      </c>
+      <c r="D790">
+        <v>13.615780000000001</v>
+      </c>
+    </row>
+    <row r="791" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A791" t="s">
+        <v>793</v>
+      </c>
+      <c r="B791">
+        <v>12.75333</v>
+      </c>
+      <c r="C791">
+        <v>1.93544</v>
+      </c>
+      <c r="D791">
+        <v>13.473229999999999</v>
+      </c>
+    </row>
+    <row r="792" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A792" t="s">
+        <v>794</v>
+      </c>
+      <c r="B792">
+        <v>12.83414</v>
+      </c>
+      <c r="C792">
+        <v>1.8008500000000001</v>
+      </c>
+      <c r="D792">
+        <v>13.497249999999999</v>
+      </c>
+    </row>
+    <row r="793" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A793" t="s">
+        <v>795</v>
+      </c>
+      <c r="B793">
+        <v>12.79743</v>
+      </c>
+      <c r="C793">
+        <v>1.83213</v>
+      </c>
+      <c r="D793">
+        <v>13.473140000000001</v>
+      </c>
+    </row>
+    <row r="794" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A794" t="s">
+        <v>796</v>
+      </c>
+      <c r="B794">
+        <v>12.685510000000001</v>
+      </c>
+      <c r="C794">
+        <v>1.94181</v>
+      </c>
+      <c r="D794">
+        <v>13.389709999999999</v>
+      </c>
+    </row>
+    <row r="795" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A795" t="s">
+        <v>797</v>
+      </c>
+      <c r="B795">
+        <v>12.88738</v>
+      </c>
+      <c r="C795">
+        <v>1.9504900000000001</v>
+      </c>
+      <c r="D795">
+        <v>13.617380000000001</v>
+      </c>
+    </row>
+    <row r="796" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A796" t="s">
+        <v>798</v>
+      </c>
+      <c r="B796">
+        <v>12.825710000000001</v>
+      </c>
+      <c r="C796">
+        <v>1.9501900000000001</v>
+      </c>
+      <c r="D796">
+        <v>13.63719</v>
+      </c>
+    </row>
+    <row r="797" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A797" t="s">
+        <v>799</v>
+      </c>
+      <c r="B797">
+        <v>12.81668</v>
+      </c>
+      <c r="C797">
+        <v>1.90802</v>
+      </c>
+      <c r="D797">
+        <v>13.694929999999999</v>
+      </c>
+    </row>
+    <row r="798" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A798" t="s">
+        <v>800</v>
+      </c>
+      <c r="B798">
+        <v>12.80462</v>
+      </c>
+      <c r="C798">
+        <v>1.9563200000000001</v>
+      </c>
+      <c r="D798">
+        <v>13.758330000000001</v>
+      </c>
+    </row>
+    <row r="799" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A799" t="s">
+        <v>801</v>
+      </c>
+      <c r="B799">
+        <v>12.81071</v>
+      </c>
+      <c r="C799">
+        <v>1.9849600000000001</v>
+      </c>
+      <c r="D799">
+        <v>13.76801</v>
+      </c>
+    </row>
+    <row r="800" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A800" t="s">
+        <v>802</v>
+      </c>
+      <c r="B800">
+        <v>12.69318</v>
+      </c>
+      <c r="C800">
+        <v>1.9661900000000001</v>
+      </c>
+      <c r="D800">
+        <v>13.433540000000001</v>
+      </c>
+    </row>
+    <row r="801" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A801" t="s">
+        <v>803</v>
+      </c>
+      <c r="B801">
+        <v>12.652419999999999</v>
+      </c>
+      <c r="C801">
+        <v>1.9567600000000001</v>
+      </c>
+      <c r="D801">
+        <v>13.346959999999999</v>
+      </c>
+    </row>
+    <row r="802" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A802" t="s">
+        <v>804</v>
+      </c>
+      <c r="B802">
+        <v>12.846080000000001</v>
+      </c>
+      <c r="C802">
+        <v>1.86957</v>
+      </c>
+      <c r="D802">
+        <v>13.494809999999999</v>
+      </c>
+    </row>
+    <row r="803" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A803" t="s">
+        <v>805</v>
+      </c>
+      <c r="B803">
+        <v>12.743790000000001</v>
+      </c>
+      <c r="C803">
+        <v>1.95591</v>
+      </c>
+      <c r="D803">
+        <v>13.382960000000001</v>
+      </c>
+    </row>
+    <row r="804" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A804" t="s">
+        <v>806</v>
+      </c>
+      <c r="B804">
+        <v>12.85467</v>
+      </c>
+      <c r="C804">
+        <v>1.8131900000000001</v>
+      </c>
+      <c r="D804">
+        <v>13.461510000000001</v>
+      </c>
+    </row>
+    <row r="805" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A805" t="s">
+        <v>807</v>
+      </c>
+      <c r="B805">
+        <v>12.868690000000001</v>
+      </c>
+      <c r="C805">
+        <v>1.86896</v>
+      </c>
+      <c r="D805">
+        <v>13.50159</v>
+      </c>
+    </row>
+    <row r="806" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A806" t="s">
+        <v>808</v>
+      </c>
+      <c r="B806">
+        <v>12.76844</v>
+      </c>
+      <c r="C806">
+        <v>1.8105100000000001</v>
+      </c>
+      <c r="D806">
+        <v>13.42764</v>
+      </c>
+    </row>
+    <row r="807" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A807" t="s">
+        <v>809</v>
+      </c>
+      <c r="B807">
+        <v>12.903840000000001</v>
+      </c>
+      <c r="C807">
+        <v>1.96268</v>
+      </c>
+      <c r="D807">
+        <v>13.50996</v>
+      </c>
+    </row>
+    <row r="808" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A808" t="s">
+        <v>810</v>
+      </c>
+      <c r="B808">
+        <v>12.809380000000001</v>
+      </c>
+      <c r="C808">
+        <v>1.85972</v>
+      </c>
+      <c r="D808">
+        <v>13.341189999999999</v>
+      </c>
+    </row>
+    <row r="809" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A809" t="s">
+        <v>811</v>
+      </c>
+      <c r="B809">
+        <v>12.69454</v>
+      </c>
+      <c r="C809">
+        <v>1.8905099999999999</v>
+      </c>
+      <c r="D809">
+        <v>13.19083</v>
+      </c>
+    </row>
+    <row r="810" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A810" t="s">
+        <v>812</v>
+      </c>
+      <c r="B810">
+        <v>12.723929999999999</v>
+      </c>
+      <c r="C810">
+        <v>1.87822</v>
+      </c>
+      <c r="D810">
+        <v>13.19322</v>
+      </c>
+    </row>
+    <row r="811" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A811" t="s">
+        <v>813</v>
+      </c>
+      <c r="B811">
+        <v>12.79213</v>
+      </c>
+      <c r="C811">
+        <v>1.8150999999999999</v>
+      </c>
+      <c r="D811">
+        <v>13.25151</v>
+      </c>
+    </row>
+    <row r="812" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A812" t="s">
+        <v>814</v>
+      </c>
+      <c r="B812">
+        <v>12.935790000000001</v>
+      </c>
+      <c r="C812">
+        <v>1.8335399999999999</v>
+      </c>
+      <c r="D812">
+        <v>13.35896</v>
+      </c>
+    </row>
+    <row r="813" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A813" t="s">
+        <v>815</v>
+      </c>
+      <c r="B813">
+        <v>12.83015</v>
+      </c>
+      <c r="C813">
+        <v>1.7161599999999999</v>
+      </c>
+      <c r="D813">
+        <v>13.219340000000001</v>
+      </c>
+    </row>
+    <row r="814" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A814" t="s">
+        <v>816</v>
+      </c>
+      <c r="B814">
+        <v>12.843360000000001</v>
+      </c>
+      <c r="C814">
+        <v>1.71726</v>
+      </c>
+      <c r="D814">
+        <v>13.21636</v>
+      </c>
+    </row>
+    <row r="815" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A815" t="s">
+        <v>817</v>
+      </c>
+      <c r="B815">
+        <v>12.81216</v>
+      </c>
+      <c r="C815">
+        <v>1.7155100000000001</v>
+      </c>
+      <c r="D815">
+        <v>13.18383</v>
+      </c>
+    </row>
+    <row r="816" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A816" t="s">
+        <v>818</v>
+      </c>
+      <c r="B816">
+        <v>12.82545</v>
+      </c>
+      <c r="C816">
+        <v>1.756</v>
+      </c>
+      <c r="D816">
+        <v>13.15156</v>
+      </c>
+    </row>
+    <row r="817" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A817" t="s">
+        <v>819</v>
+      </c>
+      <c r="B817">
+        <v>12.82269</v>
+      </c>
+      <c r="C817">
+        <v>1.7111099999999999</v>
+      </c>
+      <c r="D817">
+        <v>13.111739999999999</v>
+      </c>
+    </row>
+    <row r="818" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A818" t="s">
+        <v>820</v>
+      </c>
+      <c r="B818">
+        <v>12.763439999999999</v>
+      </c>
+      <c r="C818">
+        <v>1.85189</v>
+      </c>
+      <c r="D818">
+        <v>13.03551</v>
+      </c>
+    </row>
+    <row r="819" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A819" t="s">
+        <v>821</v>
+      </c>
+      <c r="B819">
+        <v>12.757070000000001</v>
+      </c>
+      <c r="C819">
+        <v>1.73414</v>
+      </c>
+      <c r="D819">
+        <v>12.99372</v>
+      </c>
+    </row>
+    <row r="820" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A820" t="s">
+        <v>822</v>
+      </c>
+      <c r="B820">
+        <v>12.847770000000001</v>
+      </c>
+      <c r="C820">
+        <v>1.7282299999999999</v>
+      </c>
+      <c r="D820">
+        <v>13.05756</v>
+      </c>
+    </row>
+    <row r="821" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A821" t="s">
+        <v>823</v>
+      </c>
+      <c r="B821">
+        <v>12.936579999999999</v>
+      </c>
+      <c r="C821">
+        <v>1.79965</v>
+      </c>
+      <c r="D821">
+        <v>13.642989999999999</v>
+      </c>
+    </row>
+    <row r="822" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A822" t="s">
+        <v>824</v>
+      </c>
+      <c r="B822">
+        <v>12.8583</v>
+      </c>
+      <c r="C822">
+        <v>1.72671</v>
+      </c>
+      <c r="D822">
+        <v>13.55485</v>
+      </c>
+    </row>
+    <row r="823" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A823" t="s">
+        <v>825</v>
+      </c>
+      <c r="B823">
+        <v>12.842359999999999</v>
+      </c>
+      <c r="C823">
+        <v>1.9203399999999999</v>
+      </c>
+      <c r="D823">
+        <v>13.630229999999999</v>
+      </c>
+    </row>
+    <row r="824" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A824" t="s">
+        <v>826</v>
+      </c>
+      <c r="B824">
+        <v>12.869120000000001</v>
+      </c>
+      <c r="C824">
+        <v>1.86944</v>
+      </c>
+      <c r="D824">
+        <v>13.660869999999999</v>
+      </c>
+    </row>
+    <row r="825" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A825" t="s">
+        <v>827</v>
+      </c>
+      <c r="B825">
+        <v>12.86679</v>
+      </c>
+      <c r="C825">
+        <v>1.92445</v>
+      </c>
+      <c r="D825">
+        <v>13.703580000000001</v>
+      </c>
+    </row>
+    <row r="826" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A826" t="s">
+        <v>828</v>
+      </c>
+      <c r="B826">
+        <v>12.846819999999999</v>
+      </c>
+      <c r="C826">
+        <v>1.9137500000000001</v>
+      </c>
+      <c r="D826">
+        <v>13.664260000000001</v>
+      </c>
+    </row>
+    <row r="827" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A827" t="s">
+        <v>829</v>
+      </c>
+      <c r="B827">
+        <v>12.76074</v>
+      </c>
+      <c r="C827">
+        <v>1.71915</v>
+      </c>
+      <c r="D827">
+        <v>13.490780000000001</v>
+      </c>
+    </row>
+    <row r="828" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A828" t="s">
+        <v>830</v>
+      </c>
+      <c r="B828">
+        <v>12.73701</v>
+      </c>
+      <c r="C828">
+        <v>1.79904</v>
+      </c>
+      <c r="D828">
+        <v>13.501659999999999</v>
+      </c>
+    </row>
+    <row r="829" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A829" t="s">
+        <v>831</v>
+      </c>
+      <c r="B829">
+        <v>12.898770000000001</v>
+      </c>
+      <c r="C829">
+        <v>1.9625999999999999</v>
+      </c>
+      <c r="D829">
+        <v>13.727080000000001</v>
+      </c>
+    </row>
+    <row r="830" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A830" t="s">
+        <v>832</v>
+      </c>
+      <c r="B830">
+        <v>12.85449</v>
+      </c>
+      <c r="C830">
+        <v>1.82016</v>
+      </c>
+      <c r="D830">
+        <v>13.60491</v>
+      </c>
+    </row>
+    <row r="831" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A831" t="s">
+        <v>833</v>
+      </c>
+      <c r="B831">
+        <v>12.76445</v>
+      </c>
+      <c r="C831">
+        <v>1.7512700000000001</v>
+      </c>
+      <c r="D831">
+        <v>13.48387</v>
+      </c>
+    </row>
+    <row r="832" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A832" t="s">
+        <v>834</v>
+      </c>
+      <c r="B832">
+        <v>12.82427</v>
+      </c>
+      <c r="C832">
+        <v>1.97299</v>
+      </c>
+      <c r="D832">
+        <v>13.610239999999999</v>
+      </c>
+    </row>
+    <row r="833" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A833" t="s">
+        <v>835</v>
+      </c>
+      <c r="B833">
+        <v>12.912240000000001</v>
+      </c>
+      <c r="C833">
+        <v>1.83456</v>
+      </c>
+      <c r="D833">
+        <v>13.661960000000001</v>
+      </c>
+    </row>
+    <row r="834" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A834" t="s">
+        <v>836</v>
+      </c>
+      <c r="B834">
+        <v>12.778420000000001</v>
+      </c>
+      <c r="C834">
+        <v>1.7431700000000001</v>
+      </c>
+      <c r="D834">
+        <v>13.49295</v>
+      </c>
+    </row>
+    <row r="835" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A835" t="s">
+        <v>837</v>
+      </c>
+      <c r="B835">
+        <v>12.85718</v>
+      </c>
+      <c r="C835">
+        <v>1.74882</v>
+      </c>
+      <c r="D835">
+        <v>13.582789999999999</v>
+      </c>
+    </row>
+    <row r="836" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A836" t="s">
+        <v>838</v>
+      </c>
+      <c r="B836">
+        <v>12.95523</v>
+      </c>
+      <c r="C836">
+        <v>1.8830100000000001</v>
+      </c>
+      <c r="D836">
+        <v>13.734590000000001</v>
+      </c>
+    </row>
+    <row r="837" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A837" t="s">
+        <v>839</v>
+      </c>
+      <c r="B837">
+        <v>12.857799999999999</v>
+      </c>
+      <c r="C837">
+        <v>1.91923</v>
+      </c>
+      <c r="D837">
+        <v>13.64437</v>
+      </c>
+    </row>
+    <row r="838" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A838" t="s">
+        <v>840</v>
+      </c>
+      <c r="B838">
+        <v>12.85271</v>
+      </c>
+      <c r="C838">
+        <v>1.8712599999999999</v>
+      </c>
+      <c r="D838">
+        <v>13.520619999999999</v>
+      </c>
+    </row>
+    <row r="839" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A839" t="s">
+        <v>841</v>
+      </c>
+      <c r="B839">
+        <v>12.76135</v>
+      </c>
+      <c r="C839">
+        <v>1.87812</v>
+      </c>
+      <c r="D839">
+        <v>13.374459999999999</v>
+      </c>
+    </row>
+    <row r="840" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A840" t="s">
+        <v>842</v>
+      </c>
+      <c r="B840">
+        <v>12.8969</v>
+      </c>
+      <c r="C840">
+        <v>1.8083800000000001</v>
+      </c>
+      <c r="D840">
+        <v>13.482200000000001</v>
+      </c>
+    </row>
+    <row r="841" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A841" t="s">
+        <v>843</v>
+      </c>
+      <c r="B841">
+        <v>12.85379</v>
+      </c>
+      <c r="C841">
+        <v>1.7984</v>
+      </c>
+      <c r="D841">
+        <v>13.406779999999999</v>
+      </c>
+    </row>
+    <row r="842" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A842" t="s">
+        <v>844</v>
+      </c>
+      <c r="B842">
+        <v>12.75128</v>
+      </c>
+      <c r="C842">
+        <v>1.9522200000000001</v>
+      </c>
+      <c r="D842">
+        <v>13.67787</v>
+      </c>
+    </row>
+    <row r="843" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A843" t="s">
+        <v>845</v>
+      </c>
+      <c r="B843">
+        <v>12.74657</v>
+      </c>
+      <c r="C843">
+        <v>1.72882</v>
+      </c>
+      <c r="D843">
+        <v>13.598039999999999</v>
+      </c>
+    </row>
+    <row r="844" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A844" t="s">
+        <v>846</v>
+      </c>
+      <c r="B844">
+        <v>12.93548</v>
+      </c>
+      <c r="C844">
+        <v>1.9873099999999999</v>
+      </c>
+      <c r="D844">
+        <v>13.82917</v>
+      </c>
+    </row>
+    <row r="845" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A845" t="s">
+        <v>847</v>
+      </c>
+      <c r="B845">
+        <v>12.931369999999999</v>
+      </c>
+      <c r="C845">
+        <v>1.80938</v>
+      </c>
+      <c r="D845">
+        <v>13.624000000000001</v>
+      </c>
+    </row>
+    <row r="846" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A846" t="s">
+        <v>848</v>
+      </c>
+      <c r="B846">
+        <v>12.83572</v>
+      </c>
+      <c r="C846">
+        <v>1.7219800000000001</v>
+      </c>
+      <c r="D846">
+        <v>13.350239999999999</v>
+      </c>
+    </row>
+    <row r="847" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A847" t="s">
+        <v>849</v>
+      </c>
+      <c r="B847">
+        <v>12.676959999999999</v>
+      </c>
+      <c r="C847">
+        <v>1.8967799999999999</v>
+      </c>
+      <c r="D847">
+        <v>13.189730000000001</v>
+      </c>
+    </row>
+    <row r="848" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A848" t="s">
+        <v>850</v>
+      </c>
+      <c r="B848">
+        <v>12.86251</v>
+      </c>
+      <c r="C848">
+        <v>1.87094</v>
+      </c>
+      <c r="D848">
+        <v>13.360939999999999</v>
+      </c>
+    </row>
+    <row r="849" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A849" t="s">
+        <v>851</v>
+      </c>
+      <c r="B849">
+        <v>12.857609999999999</v>
+      </c>
+      <c r="C849">
+        <v>1.7508300000000001</v>
+      </c>
+      <c r="D849">
+        <v>13.330959999999999</v>
+      </c>
+    </row>
+    <row r="850" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A850" t="s">
+        <v>852</v>
+      </c>
+      <c r="B850">
+        <v>12.74982</v>
+      </c>
+      <c r="C850">
+        <v>1.9964500000000001</v>
+      </c>
+      <c r="D850">
+        <v>13.37046</v>
+      </c>
+    </row>
+    <row r="851" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A851" t="s">
+        <v>853</v>
+      </c>
+      <c r="B851">
+        <v>12.69867</v>
+      </c>
+      <c r="C851">
+        <v>1.8057799999999999</v>
+      </c>
+      <c r="D851">
+        <v>13.420170000000001</v>
+      </c>
+    </row>
+    <row r="852" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A852" t="s">
+        <v>854</v>
+      </c>
+      <c r="B852">
+        <v>12.841559999999999</v>
+      </c>
+      <c r="C852">
+        <v>1.7531000000000001</v>
+      </c>
+      <c r="D852">
+        <v>13.39615</v>
+      </c>
+    </row>
+    <row r="853" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A853" t="s">
+        <v>855</v>
+      </c>
+      <c r="B853">
+        <v>12.737819999999999</v>
+      </c>
+      <c r="C853">
+        <v>1.72726</v>
+      </c>
+      <c r="D853">
+        <v>13.17061</v>
+      </c>
+    </row>
+    <row r="854" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A854" t="s">
+        <v>856</v>
+      </c>
+      <c r="B854">
+        <v>12.69605</v>
+      </c>
+      <c r="C854">
+        <v>1.9816400000000001</v>
+      </c>
+      <c r="D854">
+        <v>13.067410000000001</v>
+      </c>
+    </row>
+    <row r="855" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A855" t="s">
+        <v>857</v>
+      </c>
+      <c r="B855">
+        <v>12.7591</v>
+      </c>
+      <c r="C855">
+        <v>1.7094</v>
+      </c>
+      <c r="D855">
+        <v>13.06432</v>
+      </c>
+    </row>
+    <row r="856" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A856" t="s">
+        <v>858</v>
+      </c>
+      <c r="B856">
+        <v>12.820349999999999</v>
+      </c>
+      <c r="C856">
+        <v>1.7126699999999999</v>
+      </c>
+      <c r="D856">
+        <v>13.10454</v>
+      </c>
+    </row>
+    <row r="857" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A857" t="s">
+        <v>859</v>
+      </c>
+      <c r="B857">
+        <v>12.812799999999999</v>
+      </c>
+      <c r="C857">
+        <v>1.7457800000000001</v>
+      </c>
+      <c r="D857">
+        <v>13.08714</v>
+      </c>
+    </row>
+    <row r="858" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A858" t="s">
+        <v>860</v>
+      </c>
+      <c r="B858">
+        <v>12.91109</v>
+      </c>
+      <c r="C858">
+        <v>1.97177</v>
+      </c>
+      <c r="D858">
+        <v>13.266730000000001</v>
+      </c>
+    </row>
+    <row r="859" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A859" t="s">
+        <v>861</v>
+      </c>
+      <c r="B859">
+        <v>12.85838</v>
+      </c>
+      <c r="C859">
+        <v>1.77885</v>
+      </c>
+      <c r="D859">
+        <v>13.18619</v>
+      </c>
+    </row>
+    <row r="860" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A860" t="s">
+        <v>862</v>
+      </c>
+      <c r="B860">
+        <v>12.894970000000001</v>
+      </c>
+      <c r="C860">
+        <v>1.7396100000000001</v>
+      </c>
+      <c r="D860">
+        <v>13.101190000000001</v>
+      </c>
+    </row>
+    <row r="861" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A861" t="s">
+        <v>863</v>
+      </c>
+      <c r="B861">
+        <v>12.76989</v>
+      </c>
+      <c r="C861">
+        <v>1.68191</v>
+      </c>
+      <c r="D861">
+        <v>12.940200000000001</v>
+      </c>
+    </row>
+    <row r="862" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A862" t="s">
+        <v>864</v>
+      </c>
+      <c r="B862">
+        <v>12.74395</v>
+      </c>
+      <c r="C862">
+        <v>1.6429800000000001</v>
+      </c>
+      <c r="D862">
+        <v>12.929349999999999</v>
+      </c>
+    </row>
+    <row r="863" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A863" t="s">
+        <v>865</v>
+      </c>
+      <c r="B863">
+        <v>12.63491</v>
+      </c>
+      <c r="C863">
+        <v>1.9467300000000001</v>
+      </c>
+      <c r="D863">
+        <v>13.424989999999999</v>
+      </c>
+    </row>
+    <row r="864" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A864" t="s">
+        <v>866</v>
+      </c>
+      <c r="B864">
+        <v>12.89551</v>
+      </c>
+      <c r="C864">
+        <v>1.9731399999999999</v>
+      </c>
+      <c r="D864">
+        <v>13.670999999999999</v>
+      </c>
+    </row>
+    <row r="865" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A865" t="s">
+        <v>867</v>
+      </c>
+      <c r="B865">
+        <v>12.8119</v>
+      </c>
+      <c r="C865">
+        <v>1.8859999999999999</v>
+      </c>
+      <c r="D865">
+        <v>13.540089999999999</v>
+      </c>
+    </row>
+    <row r="866" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A866" t="s">
+        <v>868</v>
+      </c>
+      <c r="B866">
+        <v>12.76548</v>
+      </c>
+      <c r="C866">
+        <v>1.9897800000000001</v>
+      </c>
+      <c r="D866">
+        <v>13.54716</v>
+      </c>
+    </row>
+    <row r="867" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A867" t="s">
+        <v>869</v>
+      </c>
+      <c r="B867">
+        <v>12.83535</v>
+      </c>
+      <c r="C867">
+        <v>1.88944</v>
+      </c>
+      <c r="D867">
+        <v>13.62581</v>
+      </c>
+    </row>
+    <row r="868" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A868" t="s">
+        <v>870</v>
+      </c>
+      <c r="B868">
+        <v>12.898680000000001</v>
+      </c>
+      <c r="C868">
+        <v>1.87174</v>
+      </c>
+      <c r="D868">
+        <v>13.72831</v>
+      </c>
+    </row>
+    <row r="869" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A869" t="s">
+        <v>871</v>
+      </c>
+      <c r="B869">
+        <v>12.823930000000001</v>
+      </c>
+      <c r="C869">
+        <v>1.9699500000000001</v>
+      </c>
+      <c r="D869">
+        <v>13.75714</v>
+      </c>
+    </row>
+    <row r="870" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A870" t="s">
+        <v>872</v>
+      </c>
+      <c r="B870">
+        <v>12.857620000000001</v>
+      </c>
+      <c r="C870">
+        <v>1.70008</v>
+      </c>
+      <c r="D870">
+        <v>13.70604</v>
+      </c>
+    </row>
+    <row r="871" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A871" t="s">
+        <v>873</v>
+      </c>
+      <c r="B871">
+        <v>12.86102</v>
+      </c>
+      <c r="C871">
+        <v>1.8085100000000001</v>
+      </c>
+      <c r="D871">
+        <v>13.753450000000001</v>
+      </c>
+    </row>
+    <row r="872" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A872" t="s">
+        <v>874</v>
+      </c>
+      <c r="B872">
+        <v>12.77009</v>
+      </c>
+      <c r="C872">
+        <v>1.97071</v>
+      </c>
+      <c r="D872">
+        <v>13.736599999999999</v>
+      </c>
+    </row>
+    <row r="873" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A873" t="s">
+        <v>875</v>
+      </c>
+      <c r="B873">
+        <v>12.84901</v>
+      </c>
+      <c r="C873">
+        <v>1.8285100000000001</v>
+      </c>
+      <c r="D873">
+        <v>13.74789</v>
+      </c>
+    </row>
+    <row r="874" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A874" t="s">
+        <v>876</v>
+      </c>
+      <c r="B874">
+        <v>12.746790000000001</v>
+      </c>
+      <c r="C874">
+        <v>1.92702</v>
+      </c>
+      <c r="D874">
+        <v>13.66081</v>
+      </c>
+    </row>
+    <row r="875" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A875" t="s">
+        <v>877</v>
+      </c>
+      <c r="B875">
+        <v>12.8203</v>
+      </c>
+      <c r="C875">
+        <v>1.78843</v>
+      </c>
+      <c r="D875">
+        <v>13.63829</v>
+      </c>
+    </row>
+    <row r="876" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A876" t="s">
+        <v>878</v>
+      </c>
+      <c r="B876">
+        <v>12.85951</v>
+      </c>
+      <c r="C876">
+        <v>1.87663</v>
+      </c>
+      <c r="D876">
+        <v>13.72932</v>
+      </c>
+    </row>
+    <row r="877" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A877" t="s">
+        <v>879</v>
+      </c>
+      <c r="B877">
+        <v>12.795070000000001</v>
+      </c>
+      <c r="C877">
+        <v>1.6848700000000001</v>
+      </c>
+      <c r="D877">
+        <v>13.59308</v>
+      </c>
+    </row>
+    <row r="878" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A878" t="s">
+        <v>880</v>
+      </c>
+      <c r="B878">
+        <v>12.90241</v>
+      </c>
+      <c r="C878">
+        <v>1.86277</v>
+      </c>
+      <c r="D878">
+        <v>13.76553</v>
+      </c>
+    </row>
+    <row r="879" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A879" t="s">
+        <v>881</v>
+      </c>
+      <c r="B879">
+        <v>12.826370000000001</v>
+      </c>
+      <c r="C879">
+        <v>1.98367</v>
+      </c>
+      <c r="D879">
+        <v>13.70144</v>
+      </c>
+    </row>
+    <row r="880" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A880" t="s">
+        <v>882</v>
+      </c>
+      <c r="B880">
+        <v>12.86797</v>
+      </c>
+      <c r="C880">
+        <v>1.8485499999999999</v>
+      </c>
+      <c r="D880">
+        <v>13.65002</v>
+      </c>
+    </row>
+    <row r="881" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A881" t="s">
+        <v>883</v>
+      </c>
+      <c r="B881">
+        <v>12.750389999999999</v>
+      </c>
+      <c r="C881">
+        <v>1.9358299999999999</v>
+      </c>
+      <c r="D881">
+        <v>13.61388</v>
+      </c>
+    </row>
+    <row r="882" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A882" t="s">
+        <v>884</v>
+      </c>
+      <c r="B882">
+        <v>12.790419999999999</v>
+      </c>
+      <c r="C882">
+        <v>1.9935</v>
+      </c>
+      <c r="D882">
+        <v>13.688280000000001</v>
+      </c>
+    </row>
+    <row r="883" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A883" t="s">
+        <v>885</v>
+      </c>
+      <c r="B883">
+        <v>12.848470000000001</v>
+      </c>
+      <c r="C883">
+        <v>1.8991100000000001</v>
+      </c>
+      <c r="D883">
+        <v>13.58095</v>
+      </c>
+    </row>
+    <row r="884" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A884" t="s">
+        <v>886</v>
+      </c>
+      <c r="B884">
+        <v>12.757400000000001</v>
+      </c>
+      <c r="C884">
+        <v>1.97305</v>
+      </c>
+      <c r="D884">
+        <v>13.64927</v>
+      </c>
+    </row>
+    <row r="885" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A885" t="s">
+        <v>887</v>
+      </c>
+      <c r="B885">
+        <v>12.82821</v>
+      </c>
+      <c r="C885">
+        <v>1.75417</v>
+      </c>
+      <c r="D885">
+        <v>13.573090000000001</v>
+      </c>
+    </row>
+    <row r="886" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A886" t="s">
+        <v>888</v>
+      </c>
+      <c r="B886">
+        <v>12.838229999999999</v>
+      </c>
+      <c r="C886">
+        <v>1.7536499999999999</v>
+      </c>
+      <c r="D886">
+        <v>13.56415</v>
+      </c>
+    </row>
+    <row r="887" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A887" t="s">
+        <v>889</v>
+      </c>
+      <c r="B887">
+        <v>12.72677</v>
+      </c>
+      <c r="C887">
+        <v>1.9492</v>
+      </c>
+      <c r="D887">
+        <v>13.42778</v>
+      </c>
+    </row>
+    <row r="888" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A888" t="s">
+        <v>890</v>
+      </c>
+      <c r="B888">
+        <v>12.76066</v>
+      </c>
+      <c r="C888">
+        <v>1.7967900000000001</v>
+      </c>
+      <c r="D888">
+        <v>13.33441</v>
+      </c>
+    </row>
+    <row r="889" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A889" t="s">
+        <v>891</v>
+      </c>
+      <c r="B889">
+        <v>12.823370000000001</v>
+      </c>
+      <c r="C889">
+        <v>1.76092</v>
+      </c>
+      <c r="D889">
+        <v>13.32705</v>
+      </c>
+    </row>
+    <row r="890" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A890" t="s">
+        <v>892</v>
+      </c>
+      <c r="B890">
+        <v>12.780620000000001</v>
+      </c>
+      <c r="C890">
+        <v>1.7872600000000001</v>
+      </c>
+      <c r="D890">
+        <v>13.27094</v>
+      </c>
+    </row>
+    <row r="891" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A891" t="s">
+        <v>893</v>
+      </c>
+      <c r="B891">
+        <v>12.886889999999999</v>
+      </c>
+      <c r="C891">
+        <v>1.9490499999999999</v>
+      </c>
+      <c r="D891">
+        <v>13.414160000000001</v>
+      </c>
+    </row>
+    <row r="892" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A892" t="s">
+        <v>894</v>
+      </c>
+      <c r="B892">
+        <v>12.824159999999999</v>
+      </c>
+      <c r="C892">
+        <v>1.8228500000000001</v>
+      </c>
+      <c r="D892">
+        <v>13.30143</v>
+      </c>
+    </row>
+    <row r="893" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A893" t="s">
+        <v>895</v>
+      </c>
+      <c r="B893">
+        <v>12.8323</v>
+      </c>
+      <c r="C893">
+        <v>1.9268099999999999</v>
+      </c>
+      <c r="D893">
+        <v>13.29725</v>
+      </c>
+    </row>
+    <row r="894" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A894" t="s">
+        <v>896</v>
+      </c>
+      <c r="B894">
+        <v>12.7597</v>
+      </c>
+      <c r="C894">
+        <v>1.94737</v>
+      </c>
+      <c r="D894">
+        <v>13.22566</v>
+      </c>
+    </row>
+    <row r="895" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A895" t="s">
+        <v>897</v>
+      </c>
+      <c r="B895">
+        <v>12.8104</v>
+      </c>
+      <c r="C895">
+        <v>1.7473099999999999</v>
+      </c>
+      <c r="D895">
+        <v>13.200670000000001</v>
+      </c>
+    </row>
+    <row r="896" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A896" t="s">
+        <v>898</v>
+      </c>
+      <c r="B896">
+        <v>12.814640000000001</v>
+      </c>
+      <c r="C896">
+        <v>1.8686499999999999</v>
+      </c>
+      <c r="D896">
+        <v>13.165660000000001</v>
+      </c>
+    </row>
+    <row r="897" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A897" t="s">
+        <v>899</v>
+      </c>
+      <c r="B897">
+        <v>12.725540000000001</v>
+      </c>
+      <c r="C897">
+        <v>1.96644</v>
+      </c>
+      <c r="D897">
+        <v>13.0525</v>
+      </c>
+    </row>
+    <row r="898" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A898" t="s">
+        <v>900</v>
+      </c>
+      <c r="B898">
+        <v>12.807539999999999</v>
+      </c>
+      <c r="C898">
+        <v>1.7788900000000001</v>
+      </c>
+      <c r="D898">
+        <v>13.095039999999999</v>
+      </c>
+    </row>
+    <row r="899" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A899" t="s">
+        <v>901</v>
+      </c>
+      <c r="B899">
+        <v>12.85262</v>
+      </c>
+      <c r="C899">
+        <v>1.68032</v>
+      </c>
+      <c r="D899">
+        <v>13.10482</v>
+      </c>
+    </row>
+    <row r="900" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A900" t="s">
+        <v>902</v>
+      </c>
+      <c r="B900">
+        <v>12.747199999999999</v>
+      </c>
+      <c r="C900">
+        <v>1.7374799999999999</v>
+      </c>
+      <c r="D900">
+        <v>12.98517</v>
+      </c>
+    </row>
+    <row r="901" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A901" t="s">
+        <v>903</v>
+      </c>
+      <c r="B901">
+        <v>12.93155</v>
+      </c>
+      <c r="C901">
+        <v>1.7245200000000001</v>
+      </c>
+      <c r="D901">
+        <v>13.132759999999999</v>
+      </c>
+    </row>
+    <row r="902" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A902" t="s">
+        <v>904</v>
+      </c>
+      <c r="B902">
+        <v>12.82747</v>
+      </c>
+      <c r="C902">
+        <v>1.74278</v>
+      </c>
+      <c r="D902">
+        <v>13.01341</v>
+      </c>
+    </row>
+    <row r="903" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A903" t="s">
+        <v>905</v>
+      </c>
+      <c r="B903">
+        <v>12.88514</v>
+      </c>
+      <c r="C903">
+        <v>1.9502299999999999</v>
+      </c>
+      <c r="D903">
+        <v>13.083130000000001</v>
+      </c>
+    </row>
+    <row r="904" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A904" t="s">
+        <v>906</v>
+      </c>
+      <c r="B904">
+        <v>12.80167</v>
+      </c>
+      <c r="C904">
+        <v>1.8979200000000001</v>
+      </c>
+      <c r="D904">
+        <v>12.99546</v>
+      </c>
+    </row>
+    <row r="905" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A905" t="s">
+        <v>907</v>
+      </c>
+      <c r="B905">
+        <v>12.9742</v>
+      </c>
+      <c r="C905">
+        <v>1.74386</v>
+      </c>
+      <c r="D905">
+        <v>13.76834</v>
+      </c>
+    </row>
+    <row r="906" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A906" t="s">
+        <v>908</v>
+      </c>
+      <c r="B906">
+        <v>12.754020000000001</v>
+      </c>
+      <c r="C906">
+        <v>1.97959</v>
+      </c>
+      <c r="D906">
+        <v>13.551410000000001</v>
+      </c>
+    </row>
+    <row r="907" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A907" t="s">
+        <v>909</v>
+      </c>
+      <c r="B907">
+        <v>12.97073</v>
+      </c>
+      <c r="C907">
+        <v>1.95075</v>
+      </c>
+      <c r="D907">
+        <v>13.715210000000001</v>
+      </c>
+    </row>
+    <row r="908" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A908" t="s">
+        <v>910</v>
+      </c>
+      <c r="B908">
+        <v>12.871510000000001</v>
+      </c>
+      <c r="C908">
+        <v>1.8915500000000001</v>
+      </c>
+      <c r="D908">
+        <v>13.60148</v>
+      </c>
+    </row>
+    <row r="909" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A909" t="s">
+        <v>911</v>
+      </c>
+      <c r="B909">
+        <v>12.6867</v>
+      </c>
+      <c r="C909">
+        <v>1.98617</v>
+      </c>
+      <c r="D909">
+        <v>13.43304</v>
+      </c>
+    </row>
+    <row r="910" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A910" t="s">
+        <v>912</v>
+      </c>
+      <c r="B910">
+        <v>12.73602</v>
+      </c>
+      <c r="C910">
+        <v>1.99451</v>
+      </c>
+      <c r="D910">
+        <v>13.44572</v>
+      </c>
+    </row>
+    <row r="911" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A911" t="s">
+        <v>913</v>
+      </c>
+      <c r="B911">
+        <v>12.823</v>
+      </c>
+      <c r="C911">
+        <v>1.9653400000000001</v>
+      </c>
+      <c r="D911">
+        <v>13.47819</v>
+      </c>
+    </row>
+    <row r="912" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A912" t="s">
+        <v>914</v>
+      </c>
+      <c r="B912">
+        <v>12.85867</v>
+      </c>
+      <c r="C912">
+        <v>1.8492200000000001</v>
+      </c>
+      <c r="D912">
+        <v>13.44848</v>
+      </c>
+    </row>
+    <row r="913" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A913" t="s">
+        <v>915</v>
+      </c>
+      <c r="B913">
+        <v>12.76993</v>
+      </c>
+      <c r="C913">
+        <v>1.8649100000000001</v>
+      </c>
+      <c r="D913">
+        <v>13.33126</v>
+      </c>
+    </row>
+    <row r="914" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A914" t="s">
+        <v>916</v>
+      </c>
+      <c r="B914">
+        <v>12.88922</v>
+      </c>
+      <c r="C914">
+        <v>1.96871</v>
+      </c>
+      <c r="D914">
+        <v>13.445830000000001</v>
+      </c>
+    </row>
+    <row r="915" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A915" t="s">
+        <v>917</v>
+      </c>
+      <c r="B915">
+        <v>12.9057</v>
+      </c>
+      <c r="C915">
+        <v>1.9618599999999999</v>
+      </c>
+      <c r="D915">
+        <v>13.41493</v>
+      </c>
+    </row>
+    <row r="916" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A916" t="s">
+        <v>918</v>
+      </c>
+      <c r="B916">
+        <v>12.95454</v>
+      </c>
+      <c r="C916">
+        <v>1.75993</v>
+      </c>
+      <c r="D916">
+        <v>13.394220000000001</v>
+      </c>
+    </row>
+    <row r="917" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A917" t="s">
+        <v>919</v>
+      </c>
+      <c r="B917">
+        <v>12.733000000000001</v>
+      </c>
+      <c r="C917">
+        <v>1.73604</v>
+      </c>
+      <c r="D917">
+        <v>13.102460000000001</v>
+      </c>
+    </row>
+    <row r="918" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A918" t="s">
+        <v>920</v>
+      </c>
+      <c r="B918">
+        <v>12.84013</v>
+      </c>
+      <c r="C918">
+        <v>1.82559</v>
+      </c>
+      <c r="D918">
+        <v>13.20842</v>
+      </c>
+    </row>
+    <row r="919" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A919" t="s">
+        <v>921</v>
+      </c>
+      <c r="B919">
+        <v>12.8277</v>
+      </c>
+      <c r="C919">
+        <v>1.8965799999999999</v>
+      </c>
+      <c r="D919">
+        <v>13.19777</v>
+      </c>
+    </row>
+    <row r="920" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A920" t="s">
+        <v>922</v>
+      </c>
+      <c r="B920">
+        <v>12.81301</v>
+      </c>
+      <c r="C920">
+        <v>1.9229799999999999</v>
+      </c>
+      <c r="D920">
+        <v>13.13524</v>
+      </c>
+    </row>
+    <row r="921" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A921" t="s">
+        <v>923</v>
+      </c>
+      <c r="B921">
+        <v>12.62851</v>
+      </c>
+      <c r="C921">
+        <v>1.8838900000000001</v>
+      </c>
+      <c r="D921">
+        <v>12.92592</v>
+      </c>
+    </row>
+    <row r="922" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A922" t="s">
+        <v>924</v>
+      </c>
+      <c r="B922">
+        <v>12.89634</v>
+      </c>
+      <c r="C922">
+        <v>1.7942899999999999</v>
+      </c>
+      <c r="D922">
+        <v>13.149430000000001</v>
+      </c>
+    </row>
+    <row r="923" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A923" t="s">
+        <v>925</v>
+      </c>
+      <c r="B923">
+        <v>12.690200000000001</v>
+      </c>
+      <c r="C923">
+        <v>1.8166500000000001</v>
+      </c>
+      <c r="D923">
+        <v>12.927440000000001</v>
+      </c>
+    </row>
+    <row r="924" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A924" t="s">
+        <v>926</v>
+      </c>
+      <c r="B924">
+        <v>12.69209</v>
+      </c>
+      <c r="C924">
+        <v>1.94163</v>
+      </c>
+      <c r="D924">
+        <v>12.914859999999999</v>
+      </c>
+    </row>
+    <row r="925" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A925" t="s">
+        <v>927</v>
+      </c>
+      <c r="B925">
+        <v>12.86999</v>
+      </c>
+      <c r="C925">
+        <v>1.76864</v>
+      </c>
+      <c r="D925">
+        <v>13.089639999999999</v>
+      </c>
+    </row>
+    <row r="926" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A926" t="s">
+        <v>928</v>
+      </c>
+      <c r="B926">
+        <v>12.793329999999999</v>
+      </c>
+      <c r="C926">
+        <v>1.8128899999999999</v>
+      </c>
+      <c r="D926">
+        <v>13.39498</v>
+      </c>
+    </row>
+    <row r="927" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A927" t="s">
+        <v>929</v>
+      </c>
+      <c r="B927">
+        <v>12.85746</v>
+      </c>
+      <c r="C927">
+        <v>1.81555</v>
+      </c>
+      <c r="D927">
+        <v>13.42515</v>
+      </c>
+    </row>
+    <row r="928" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A928" t="s">
+        <v>930</v>
+      </c>
+      <c r="B928">
+        <v>12.83197</v>
+      </c>
+      <c r="C928">
+        <v>1.7475799999999999</v>
+      </c>
+      <c r="D928">
+        <v>13.337</v>
+      </c>
+    </row>
+    <row r="929" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A929" t="s">
+        <v>931</v>
+      </c>
+      <c r="B929">
+        <v>12.793369999999999</v>
+      </c>
+      <c r="C929">
+        <v>1.9696899999999999</v>
+      </c>
+      <c r="D929">
+        <v>13.33521</v>
+      </c>
+    </row>
+    <row r="930" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A930" t="s">
+        <v>932</v>
+      </c>
+      <c r="B930">
+        <v>12.905900000000001</v>
+      </c>
+      <c r="C930">
+        <v>1.78444</v>
+      </c>
+      <c r="D930">
+        <v>13.3802</v>
+      </c>
+    </row>
+    <row r="931" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A931" t="s">
+        <v>933</v>
+      </c>
+      <c r="B931">
+        <v>12.891489999999999</v>
+      </c>
+      <c r="C931">
+        <v>1.80067</v>
+      </c>
+      <c r="D931">
+        <v>13.32795</v>
+      </c>
+    </row>
+    <row r="932" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A932" t="s">
+        <v>934</v>
+      </c>
+      <c r="B932">
+        <v>12.810420000000001</v>
+      </c>
+      <c r="C932">
+        <v>1.7698</v>
+      </c>
+      <c r="D932">
+        <v>13.23099</v>
+      </c>
+    </row>
+    <row r="933" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A933" t="s">
+        <v>935</v>
+      </c>
+      <c r="B933">
+        <v>12.95355</v>
+      </c>
+      <c r="C933">
+        <v>1.74305</v>
+      </c>
+      <c r="D933">
+        <v>13.38274</v>
+      </c>
+    </row>
+    <row r="934" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A934" t="s">
+        <v>936</v>
+      </c>
+      <c r="B934">
+        <v>12.81697</v>
+      </c>
+      <c r="C934">
+        <v>1.9384300000000001</v>
+      </c>
+      <c r="D934">
+        <v>13.29302</v>
+      </c>
+    </row>
+    <row r="935" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A935" t="s">
+        <v>937</v>
+      </c>
+      <c r="B935">
+        <v>12.90644</v>
+      </c>
+      <c r="C935">
+        <v>1.8334999999999999</v>
+      </c>
+      <c r="D935">
+        <v>13.354649999999999</v>
+      </c>
+    </row>
+    <row r="936" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A936" t="s">
+        <v>938</v>
+      </c>
+      <c r="B936">
+        <v>12.661519999999999</v>
+      </c>
+      <c r="C936">
+        <v>1.7894600000000001</v>
+      </c>
+      <c r="D936">
+        <v>13.09549</v>
+      </c>
+    </row>
+    <row r="937" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A937" t="s">
+        <v>939</v>
+      </c>
+      <c r="B937">
+        <v>12.75774</v>
+      </c>
+      <c r="C937">
+        <v>1.8272699999999999</v>
+      </c>
+      <c r="D937">
+        <v>13.169219999999999</v>
+      </c>
+    </row>
+    <row r="938" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A938" t="s">
+        <v>940</v>
+      </c>
+      <c r="B938">
+        <v>12.83245</v>
+      </c>
+      <c r="C938">
+        <v>1.8161400000000001</v>
+      </c>
+      <c r="D938">
+        <v>13.14753</v>
+      </c>
+    </row>
+    <row r="939" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A939" t="s">
+        <v>941</v>
+      </c>
+      <c r="B939">
+        <v>12.733040000000001</v>
+      </c>
+      <c r="C939">
+        <v>1.77494</v>
+      </c>
+      <c r="D939">
+        <v>12.99408</v>
+      </c>
+    </row>
+    <row r="940" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A940" t="s">
+        <v>942</v>
+      </c>
+      <c r="B940">
+        <v>12.843970000000001</v>
+      </c>
+      <c r="C940">
+        <v>1.8575299999999999</v>
+      </c>
+      <c r="D940">
+        <v>13.111420000000001</v>
+      </c>
+    </row>
+    <row r="941" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A941" t="s">
+        <v>943</v>
+      </c>
+      <c r="B941">
+        <v>12.81316</v>
+      </c>
+      <c r="C941">
+        <v>1.89358</v>
+      </c>
+      <c r="D941">
+        <v>13.083209999999999</v>
+      </c>
+    </row>
+    <row r="942" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A942" t="s">
+        <v>944</v>
+      </c>
+      <c r="B942">
+        <v>12.88171</v>
+      </c>
+      <c r="C942">
+        <v>1.91388</v>
+      </c>
+      <c r="D942">
+        <v>13.13246</v>
+      </c>
+    </row>
+    <row r="943" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A943" t="s">
+        <v>945</v>
+      </c>
+      <c r="B943">
+        <v>12.739470000000001</v>
+      </c>
+      <c r="C943">
+        <v>1.86938</v>
+      </c>
+      <c r="D943">
+        <v>12.9483</v>
+      </c>
+    </row>
+    <row r="944" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A944" t="s">
+        <v>946</v>
+      </c>
+      <c r="B944">
+        <v>12.67658</v>
+      </c>
+      <c r="C944">
+        <v>1.85568</v>
+      </c>
+      <c r="D944">
+        <v>12.85727</v>
+      </c>
+    </row>
+    <row r="945" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A945" t="s">
+        <v>947</v>
+      </c>
+      <c r="B945">
+        <v>12.791309999999999</v>
+      </c>
+      <c r="C945">
+        <v>1.8319300000000001</v>
+      </c>
+      <c r="D945">
+        <v>12.96435</v>
+      </c>
+    </row>
+    <row r="946" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A946" t="s">
+        <v>948</v>
+      </c>
+      <c r="B946">
+        <v>12.878819999999999</v>
+      </c>
+      <c r="C946">
+        <v>1.9222900000000001</v>
+      </c>
+      <c r="D946">
+        <v>13.08315</v>
+      </c>
+    </row>
+    <row r="947" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A947" t="s">
+        <v>949</v>
+      </c>
+      <c r="B947">
+        <v>12.954000000000001</v>
+      </c>
+      <c r="C947">
+        <v>1.9034899999999999</v>
+      </c>
+      <c r="D947">
+        <v>13.72401</v>
+      </c>
+    </row>
+    <row r="948" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A948" t="s">
+        <v>950</v>
+      </c>
+      <c r="B948">
+        <v>12.728</v>
+      </c>
+      <c r="C948">
+        <v>1.9381200000000001</v>
+      </c>
+      <c r="D948">
+        <v>13.52918</v>
+      </c>
+    </row>
+    <row r="949" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A949" t="s">
+        <v>951</v>
+      </c>
+      <c r="B949">
+        <v>12.86504</v>
+      </c>
+      <c r="C949">
+        <v>1.95008</v>
+      </c>
+      <c r="D949">
+        <v>13.67671</v>
+      </c>
+    </row>
+    <row r="950" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A950" t="s">
+        <v>952</v>
+      </c>
+      <c r="B950">
+        <v>12.72434</v>
+      </c>
+      <c r="C950">
+        <v>1.79358</v>
+      </c>
+      <c r="D950">
+        <v>13.4558</v>
+      </c>
+    </row>
+    <row r="951" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A951" t="s">
+        <v>953</v>
+      </c>
+      <c r="B951">
+        <v>12.863329999999999</v>
+      </c>
+      <c r="C951">
+        <v>1.93085</v>
+      </c>
+      <c r="D951">
+        <v>13.638479999999999</v>
+      </c>
+    </row>
+    <row r="952" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A952" t="s">
+        <v>954</v>
+      </c>
+      <c r="B952">
+        <v>12.91414</v>
+      </c>
+      <c r="C952">
+        <v>1.77932</v>
+      </c>
+      <c r="D952">
+        <v>13.62387</v>
+      </c>
+    </row>
+    <row r="953" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A953" t="s">
+        <v>955</v>
+      </c>
+      <c r="B953">
+        <v>12.81691</v>
+      </c>
+      <c r="C953">
+        <v>1.93971</v>
+      </c>
+      <c r="D953">
+        <v>13.60515</v>
+      </c>
+    </row>
+    <row r="954" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A954" t="s">
+        <v>956</v>
+      </c>
+      <c r="B954">
+        <v>12.983510000000001</v>
+      </c>
+      <c r="C954">
+        <v>1.94051</v>
+      </c>
+      <c r="D954">
+        <v>13.80556</v>
+      </c>
+    </row>
+    <row r="955" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A955" t="s">
+        <v>957</v>
+      </c>
+      <c r="B955">
+        <v>12.881349999999999</v>
+      </c>
+      <c r="C955">
+        <v>1.8960699999999999</v>
+      </c>
+      <c r="D955">
+        <v>13.78763</v>
+      </c>
+    </row>
+    <row r="956" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A956" t="s">
+        <v>958</v>
+      </c>
+      <c r="B956">
+        <v>12.60458</v>
+      </c>
+      <c r="C956">
+        <v>1.90707</v>
+      </c>
+      <c r="D956">
+        <v>13.539</v>
+      </c>
+    </row>
+    <row r="957" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A957" t="s">
+        <v>959</v>
+      </c>
+      <c r="B957">
+        <v>12.83991</v>
+      </c>
+      <c r="C957">
+        <v>1.99309</v>
+      </c>
+      <c r="D957">
+        <v>13.81082</v>
+      </c>
+    </row>
+    <row r="958" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A958" t="s">
+        <v>960</v>
+      </c>
+      <c r="B958">
+        <v>12.817640000000001</v>
+      </c>
+      <c r="C958">
+        <v>1.96113</v>
+      </c>
+      <c r="D958">
+        <v>13.766400000000001</v>
+      </c>
+    </row>
+    <row r="959" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A959" t="s">
+        <v>961</v>
+      </c>
+      <c r="B959">
+        <v>12.804169999999999</v>
+      </c>
+      <c r="C959">
+        <v>1.8859600000000001</v>
+      </c>
+      <c r="D959">
+        <v>13.68352</v>
+      </c>
+    </row>
+    <row r="960" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A960" t="s">
+        <v>962</v>
+      </c>
+      <c r="B960">
+        <v>12.797890000000001</v>
+      </c>
+      <c r="C960">
+        <v>1.91025</v>
+      </c>
+      <c r="D960">
+        <v>13.668850000000001</v>
+      </c>
+    </row>
+    <row r="961" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A961" t="s">
+        <v>963</v>
+      </c>
+      <c r="B961">
+        <v>12.760770000000001</v>
+      </c>
+      <c r="C961">
+        <v>1.96655</v>
+      </c>
+      <c r="D961">
+        <v>13.659940000000001</v>
+      </c>
+    </row>
+    <row r="962" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A962" t="s">
+        <v>964</v>
+      </c>
+      <c r="B962">
+        <v>12.82888</v>
+      </c>
+      <c r="C962">
+        <v>1.9926999999999999</v>
+      </c>
+      <c r="D962">
+        <v>13.7384</v>
+      </c>
+    </row>
+    <row r="963" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A963" t="s">
+        <v>965</v>
+      </c>
+      <c r="B963">
+        <v>12.727259999999999</v>
+      </c>
+      <c r="C963">
+        <v>1.8709100000000001</v>
+      </c>
+      <c r="D963">
+        <v>13.58497</v>
+      </c>
+    </row>
+    <row r="964" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A964" t="s">
+        <v>966</v>
+      </c>
+      <c r="B964">
+        <v>12.89866</v>
+      </c>
+      <c r="C964">
+        <v>1.96682</v>
+      </c>
+      <c r="D964">
+        <v>13.79857</v>
+      </c>
+    </row>
+    <row r="965" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A965" t="s">
+        <v>967</v>
+      </c>
+      <c r="B965">
+        <v>12.6975</v>
+      </c>
+      <c r="C965">
+        <v>1.96146</v>
+      </c>
+      <c r="D965">
+        <v>13.552619999999999</v>
+      </c>
+    </row>
+    <row r="966" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A966" t="s">
+        <v>968</v>
+      </c>
+      <c r="B966">
+        <v>12.85164</v>
+      </c>
+      <c r="C966">
+        <v>1.8278300000000001</v>
+      </c>
+      <c r="D966">
+        <v>13.6411</v>
+      </c>
+    </row>
+    <row r="967" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A967" t="s">
+        <v>969</v>
+      </c>
+      <c r="B967">
+        <v>12.750920000000001</v>
+      </c>
+      <c r="C967">
+        <v>1.99142</v>
+      </c>
+      <c r="D967">
+        <v>13.46156</v>
+      </c>
+    </row>
+    <row r="968" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A968" t="s">
+        <v>970</v>
+      </c>
+      <c r="B968">
+        <v>12.806789999999999</v>
+      </c>
+      <c r="C968">
+        <v>1.8990400000000001</v>
+      </c>
+      <c r="D968">
+        <v>13.635999999999999</v>
+      </c>
+    </row>
+    <row r="969" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A969" t="s">
+        <v>971</v>
+      </c>
+      <c r="B969">
+        <v>12.934530000000001</v>
+      </c>
+      <c r="C969">
+        <v>1.8950100000000001</v>
+      </c>
+      <c r="D969">
+        <v>13.74414</v>
+      </c>
+    </row>
+    <row r="970" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A970" t="s">
+        <v>972</v>
+      </c>
+      <c r="B970">
+        <v>12.74431</v>
+      </c>
+      <c r="C970">
+        <v>1.8390599999999999</v>
+      </c>
+      <c r="D970">
+        <v>13.534230000000001</v>
+      </c>
+    </row>
+    <row r="971" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A971" t="s">
+        <v>973</v>
+      </c>
+      <c r="B971">
+        <v>12.888579999999999</v>
+      </c>
+      <c r="C971">
+        <v>1.82097</v>
+      </c>
+      <c r="D971">
+        <v>13.643560000000001</v>
+      </c>
+    </row>
+    <row r="972" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A972" t="s">
+        <v>974</v>
+      </c>
+      <c r="B972">
+        <v>12.50535</v>
+      </c>
+      <c r="C972">
+        <v>1.9099900000000001</v>
+      </c>
+      <c r="D972">
+        <v>13.292809999999999</v>
+      </c>
+    </row>
+    <row r="973" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A973" t="s">
+        <v>975</v>
+      </c>
+      <c r="B973">
+        <v>12.80681</v>
+      </c>
+      <c r="C973">
+        <v>1.98553</v>
+      </c>
+      <c r="D973">
+        <v>13.613099999999999</v>
+      </c>
+    </row>
+    <row r="974" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A974" t="s">
+        <v>976</v>
+      </c>
+      <c r="B974">
+        <v>12.837479999999999</v>
+      </c>
+      <c r="C974">
+        <v>1.8002400000000001</v>
+      </c>
+      <c r="D974">
+        <v>13.55626</v>
+      </c>
+    </row>
+    <row r="975" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A975" t="s">
+        <v>977</v>
+      </c>
+      <c r="B975">
+        <v>12.8241</v>
+      </c>
+      <c r="C975">
+        <v>1.8366199999999999</v>
+      </c>
+      <c r="D975">
+        <v>13.53332</v>
+      </c>
+    </row>
+    <row r="976" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A976" t="s">
+        <v>978</v>
+      </c>
+      <c r="B976">
+        <v>12.500299999999999</v>
+      </c>
+      <c r="C976">
+        <v>1.9518500000000001</v>
+      </c>
+      <c r="D976">
+        <v>13.231999999999999</v>
+      </c>
+    </row>
+    <row r="977" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A977" t="s">
+        <v>979</v>
+      </c>
+      <c r="B977">
+        <v>12.494540000000001</v>
+      </c>
+      <c r="C977">
+        <v>1.9521500000000001</v>
+      </c>
+      <c r="D977">
+        <v>13.18192</v>
+      </c>
+    </row>
+    <row r="978" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A978" t="s">
+        <v>980</v>
+      </c>
+      <c r="B978">
+        <v>12.52186</v>
+      </c>
+      <c r="C978">
+        <v>1.87948</v>
+      </c>
+      <c r="D978">
+        <v>13.223800000000001</v>
+      </c>
+    </row>
+    <row r="979" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A979" t="s">
+        <v>981</v>
+      </c>
+      <c r="B979">
+        <v>12.53603</v>
+      </c>
+      <c r="C979">
+        <v>1.9414499999999999</v>
+      </c>
+      <c r="D979">
+        <v>13.31818</v>
+      </c>
+    </row>
+    <row r="980" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A980" t="s">
+        <v>982</v>
+      </c>
+      <c r="B980">
+        <v>12.4513</v>
+      </c>
+      <c r="C980">
+        <v>1.8618699999999999</v>
+      </c>
+      <c r="D980">
+        <v>13.21819</v>
+      </c>
+    </row>
+    <row r="981" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A981" t="s">
+        <v>983</v>
+      </c>
+      <c r="B981">
+        <v>12.473940000000001</v>
+      </c>
+      <c r="C981">
+        <v>1.7975399999999999</v>
+      </c>
+      <c r="D981">
+        <v>13.23353</v>
+      </c>
+    </row>
+    <row r="982" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A982" t="s">
+        <v>984</v>
+      </c>
+      <c r="B982">
+        <v>12.49531</v>
+      </c>
+      <c r="C982">
+        <v>1.97159</v>
+      </c>
+      <c r="D982">
+        <v>13.339090000000001</v>
+      </c>
+    </row>
+    <row r="983" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A983" t="s">
+        <v>985</v>
+      </c>
+      <c r="B983">
+        <v>12.499219999999999</v>
+      </c>
+      <c r="C983">
+        <v>1.87198</v>
+      </c>
+      <c r="D983">
+        <v>13.33839</v>
+      </c>
+    </row>
+    <row r="984" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A984" t="s">
+        <v>986</v>
+      </c>
+      <c r="B984">
+        <v>12.51651</v>
+      </c>
+      <c r="C984">
+        <v>1.8229599999999999</v>
+      </c>
+      <c r="D984">
+        <v>13.383710000000001</v>
+      </c>
+    </row>
+    <row r="985" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A985" t="s">
+        <v>987</v>
+      </c>
+      <c r="B985">
+        <v>12.50713</v>
+      </c>
+      <c r="C985">
+        <v>1.8710599999999999</v>
+      </c>
+      <c r="D985">
+        <v>13.39179</v>
+      </c>
+    </row>
+    <row r="986" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A986" t="s">
+        <v>988</v>
+      </c>
+      <c r="B986">
+        <v>12.49892</v>
+      </c>
+      <c r="C986">
+        <v>1.8850800000000001</v>
+      </c>
+      <c r="D986">
+        <v>13.386240000000001</v>
+      </c>
+    </row>
+    <row r="987" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A987" t="s">
+        <v>989</v>
+      </c>
+      <c r="B987">
+        <v>12.52525</v>
+      </c>
+      <c r="C987">
+        <v>1.87487</v>
+      </c>
+      <c r="D987">
+        <v>13.40133</v>
+      </c>
+    </row>
+    <row r="988" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A988" t="s">
+        <v>990</v>
+      </c>
+      <c r="B988">
+        <v>12.457179999999999</v>
+      </c>
+      <c r="C988">
+        <v>1.8557600000000001</v>
+      </c>
+      <c r="D988">
+        <v>13.272489999999999</v>
+      </c>
+    </row>
+    <row r="989" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A989" t="s">
+        <v>991</v>
+      </c>
+      <c r="B989">
+        <v>12.44406</v>
+      </c>
+      <c r="C989">
+        <v>1.9027700000000001</v>
+      </c>
+      <c r="D989">
+        <v>13.323650000000001</v>
+      </c>
+    </row>
+    <row r="990" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A990" t="s">
+        <v>992</v>
+      </c>
+      <c r="B990">
+        <v>12.77914</v>
+      </c>
+      <c r="C990">
+        <v>1.9408300000000001</v>
+      </c>
+      <c r="D990">
+        <v>13.42151</v>
+      </c>
+    </row>
+    <row r="991" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A991" t="s">
+        <v>993</v>
+      </c>
+      <c r="B991">
+        <v>12.36979</v>
+      </c>
+      <c r="C991">
+        <v>1.9117599999999999</v>
+      </c>
+      <c r="D991">
+        <v>12.999599999999999</v>
+      </c>
+    </row>
+    <row r="992" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A992" t="s">
+        <v>994</v>
+      </c>
+      <c r="B992">
+        <v>12.47776</v>
+      </c>
+      <c r="C992">
+        <v>1.7504500000000001</v>
+      </c>
+      <c r="D992">
+        <v>13.04102</v>
+      </c>
+    </row>
+    <row r="993" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A993" t="s">
+        <v>995</v>
+      </c>
+      <c r="B993">
+        <v>12.493130000000001</v>
+      </c>
+      <c r="C993">
+        <v>1.77799</v>
+      </c>
+      <c r="D993">
+        <v>13.050240000000001</v>
+      </c>
+    </row>
+    <row r="994" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A994" t="s">
+        <v>996</v>
+      </c>
+      <c r="B994">
+        <v>12.503410000000001</v>
+      </c>
+      <c r="C994">
+        <v>1.9170100000000001</v>
+      </c>
+      <c r="D994">
+        <v>13.111700000000001</v>
+      </c>
+    </row>
+    <row r="995" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A995" t="s">
+        <v>997</v>
+      </c>
+      <c r="B995">
+        <v>12.884119999999999</v>
+      </c>
+      <c r="C995">
+        <v>1.8866000000000001</v>
+      </c>
+      <c r="D995">
+        <v>13.4682</v>
+      </c>
+    </row>
+    <row r="996" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A996" t="s">
+        <v>998</v>
+      </c>
+      <c r="B996">
+        <v>12.812720000000001</v>
+      </c>
+      <c r="C996">
+        <v>1.7896300000000001</v>
+      </c>
+      <c r="D996">
+        <v>13.34294</v>
+      </c>
+    </row>
+    <row r="997" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A997" t="s">
+        <v>999</v>
+      </c>
+      <c r="B997">
+        <v>12.47071</v>
+      </c>
+      <c r="C997">
+        <v>1.8698900000000001</v>
+      </c>
+      <c r="D997">
+        <v>12.99757</v>
+      </c>
+    </row>
+    <row r="998" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A998" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B998">
+        <v>12.49605</v>
+      </c>
+      <c r="C998">
+        <v>1.77867</v>
+      </c>
+      <c r="D998">
+        <v>12.974589999999999</v>
+      </c>
+    </row>
+    <row r="999" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A999" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B999">
+        <v>12.720420000000001</v>
+      </c>
+      <c r="C999">
+        <v>1.7308399999999999</v>
+      </c>
+      <c r="D999">
+        <v>13.10535</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1000" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B1000">
+        <v>12.442030000000001</v>
+      </c>
+      <c r="C1000">
+        <v>1.8439099999999999</v>
+      </c>
+      <c r="D1000">
+        <v>12.771459999999999</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1001" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B1001">
+        <v>12.911390000000001</v>
+      </c>
+      <c r="C1001">
+        <v>1.7444299999999999</v>
+      </c>
+      <c r="D1001">
+        <v>13.181179999999999</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1002" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B1002">
+        <v>12.931520000000001</v>
+      </c>
+      <c r="C1002">
+        <v>1.9885699999999999</v>
+      </c>
+      <c r="D1002">
+        <v>13.22734</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1003" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B1003">
+        <v>12.975289999999999</v>
+      </c>
+      <c r="C1003">
+        <v>1.93936</v>
+      </c>
+      <c r="D1003">
+        <v>13.25169</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1004" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B1004">
+        <v>12.90376</v>
+      </c>
+      <c r="C1004">
+        <v>1.98583</v>
+      </c>
+      <c r="D1004">
+        <v>13.154159999999999</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1005" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B1005">
+        <v>12.95973</v>
+      </c>
+      <c r="C1005">
+        <v>1.8969199999999999</v>
+      </c>
+      <c r="D1005">
+        <v>13.17367</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1006" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B1006">
+        <v>12.93009</v>
+      </c>
+      <c r="C1006">
+        <v>1.81162</v>
+      </c>
+      <c r="D1006">
+        <v>13.113440000000001</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1007" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B1007">
+        <v>12.92708</v>
+      </c>
+      <c r="C1007">
+        <v>1.9584299999999999</v>
+      </c>
+      <c r="D1007">
+        <v>13.11223</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1008" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B1008">
+        <v>12.96485</v>
+      </c>
+      <c r="C1008">
+        <v>1.9347399999999999</v>
+      </c>
+      <c r="D1008">
+        <v>13.14629</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1009" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B1009">
+        <v>12.930949999999999</v>
+      </c>
+      <c r="C1009">
+        <v>1.83405</v>
+      </c>
+      <c r="D1009">
+        <v>13.10591</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1010" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B1010">
+        <v>12.93736</v>
+      </c>
+      <c r="C1010">
+        <v>1.9943599999999999</v>
+      </c>
+      <c r="D1010">
+        <v>13.61955</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1011" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B1011">
+        <v>12.99929</v>
+      </c>
+      <c r="C1011">
+        <v>1.97305</v>
+      </c>
+      <c r="D1011">
+        <v>13.6769</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1012" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B1012">
+        <v>12.956490000000001</v>
+      </c>
+      <c r="C1012">
+        <v>1.8189</v>
+      </c>
+      <c r="D1012">
+        <v>13.554449999999999</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1013" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B1013">
+        <v>12.89386</v>
+      </c>
+      <c r="C1013">
+        <v>1.9739899999999999</v>
+      </c>
+      <c r="D1013">
+        <v>13.55505</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1014" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B1014">
+        <v>12.95321</v>
+      </c>
+      <c r="C1014">
+        <v>1.9641599999999999</v>
+      </c>
+      <c r="D1014">
+        <v>13.577030000000001</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1015" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B1015">
+        <v>12.94727</v>
+      </c>
+      <c r="C1015">
+        <v>1.8885799999999999</v>
+      </c>
+      <c r="D1015">
+        <v>13.53636</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1016" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B1016">
+        <v>12.93056</v>
+      </c>
+      <c r="C1016">
+        <v>1.99146</v>
+      </c>
+      <c r="D1016">
+        <v>13.551399999999999</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1017" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B1017">
+        <v>12.98672</v>
+      </c>
+      <c r="C1017">
+        <v>1.88348</v>
+      </c>
+      <c r="D1017">
+        <v>13.551830000000001</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1018" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B1018">
+        <v>12.93181</v>
+      </c>
+      <c r="C1018">
+        <v>1.89272</v>
+      </c>
+      <c r="D1018">
+        <v>13.505979999999999</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1019" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B1019">
+        <v>13.10277</v>
+      </c>
+      <c r="C1019">
+        <v>1.9912799999999999</v>
+      </c>
+      <c r="D1019">
+        <v>13.699400000000001</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1020" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B1020">
+        <v>12.93196</v>
+      </c>
+      <c r="C1020">
+        <v>1.7825899999999999</v>
+      </c>
+      <c r="D1020">
+        <v>13.45534</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1021" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B1021">
+        <v>12.98856</v>
+      </c>
+      <c r="C1021">
+        <v>1.85825</v>
+      </c>
+      <c r="D1021">
+        <v>13.509919999999999</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1022" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B1022">
+        <v>12.95903</v>
+      </c>
+      <c r="C1022">
+        <v>1.7982</v>
+      </c>
+      <c r="D1022">
+        <v>13.40766</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1023" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B1023">
+        <v>12.96918</v>
+      </c>
+      <c r="C1023">
+        <v>1.9660299999999999</v>
+      </c>
+      <c r="D1023">
+        <v>13.41441</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1024" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B1024">
+        <v>12.917439999999999</v>
+      </c>
+      <c r="C1024">
+        <v>1.86093</v>
+      </c>
+      <c r="D1024">
+        <v>13.31894</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1025" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B1025">
+        <v>12.944419999999999</v>
+      </c>
+      <c r="C1025">
+        <v>1.9260699999999999</v>
+      </c>
+      <c r="D1025">
+        <v>13.340630000000001</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1026" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B1026">
+        <v>12.962999999999999</v>
+      </c>
+      <c r="C1026">
+        <v>1.88243</v>
+      </c>
+      <c r="D1026">
+        <v>13.30353</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1027" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B1027">
+        <v>12.932309999999999</v>
+      </c>
+      <c r="C1027">
+        <v>1.9721500000000001</v>
+      </c>
+      <c r="D1027">
+        <v>13.283189999999999</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1028" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B1028">
+        <v>12.936400000000001</v>
+      </c>
+      <c r="C1028">
+        <v>1.84006</v>
+      </c>
+      <c r="D1028">
+        <v>13.23883</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1029" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B1029">
+        <v>12.949020000000001</v>
+      </c>
+      <c r="C1029">
+        <v>1.92987</v>
+      </c>
+      <c r="D1029">
+        <v>13.2577</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1030" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B1030">
+        <v>12.907220000000001</v>
+      </c>
+      <c r="C1030">
+        <v>1.9222900000000001</v>
+      </c>
+      <c r="D1030">
+        <v>13.190910000000001</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1031" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B1031">
+        <v>12.95045</v>
+      </c>
+      <c r="C1031">
+        <v>1.98163</v>
+      </c>
+      <c r="D1031">
+        <v>13.87538</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1032" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B1032">
+        <v>12.924189999999999</v>
+      </c>
+      <c r="C1032">
+        <v>1.96353</v>
+      </c>
+      <c r="D1032">
+        <v>13.7575</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1033" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B1033">
+        <v>12.96903</v>
+      </c>
+      <c r="C1033">
+        <v>1.9146099999999999</v>
+      </c>
+      <c r="D1033">
+        <v>13.72607</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1034" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B1034">
+        <v>13.10092</v>
+      </c>
+      <c r="C1034">
+        <v>1.8999299999999999</v>
+      </c>
+      <c r="D1034">
+        <v>13.8749</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1035" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B1035">
+        <v>13.003119999999999</v>
+      </c>
+      <c r="C1035">
+        <v>1.8645799999999999</v>
+      </c>
+      <c r="D1035">
+        <v>13.764139999999999</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1036" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B1036">
+        <v>12.97897</v>
+      </c>
+      <c r="C1036">
+        <v>1.8865799999999999</v>
+      </c>
+      <c r="D1036">
+        <v>13.720420000000001</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1037" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B1037">
+        <v>12.965210000000001</v>
+      </c>
+      <c r="C1037">
+        <v>1.99417</v>
+      </c>
+      <c r="D1037">
+        <v>13.65976</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1038" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B1038">
+        <v>12.957269999999999</v>
+      </c>
+      <c r="C1038">
+        <v>1.9759100000000001</v>
+      </c>
+      <c r="D1038">
+        <v>13.626429999999999</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1039" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B1039">
+        <v>12.96026</v>
+      </c>
+      <c r="C1039">
+        <v>1.8641000000000001</v>
+      </c>
+      <c r="D1039">
+        <v>13.59456</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1040" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B1040">
+        <v>12.92306</v>
+      </c>
+      <c r="C1040">
+        <v>1.94668</v>
+      </c>
+      <c r="D1040">
+        <v>13.52004</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1041" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B1041">
+        <v>12.9215</v>
+      </c>
+      <c r="C1041">
+        <v>1.9959800000000001</v>
+      </c>
+      <c r="D1041">
+        <v>13.4917</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1042" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B1042">
+        <v>12.93439</v>
+      </c>
+      <c r="C1042">
+        <v>1.97715</v>
+      </c>
+      <c r="D1042">
+        <v>13.463620000000001</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1043" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B1043">
+        <v>12.95571</v>
+      </c>
+      <c r="C1043">
+        <v>1.93025</v>
+      </c>
+      <c r="D1043">
+        <v>13.470330000000001</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1044" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B1044">
+        <v>13.004379999999999</v>
+      </c>
+      <c r="C1044">
+        <v>1.9354</v>
+      </c>
+      <c r="D1044">
+        <v>13.472939999999999</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1045" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B1045">
+        <v>12.988860000000001</v>
+      </c>
+      <c r="C1045">
+        <v>1.7695399999999999</v>
+      </c>
+      <c r="D1045">
+        <v>13.36448</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1046" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B1046">
+        <v>12.958830000000001</v>
+      </c>
+      <c r="C1046">
+        <v>1.7726900000000001</v>
+      </c>
+      <c r="D1046">
+        <v>13.27861</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1047" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B1047">
+        <v>12.93122</v>
+      </c>
+      <c r="C1047">
+        <v>1.9582200000000001</v>
+      </c>
+      <c r="D1047">
+        <v>13.241300000000001</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1048" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B1048">
+        <v>13.063280000000001</v>
+      </c>
+      <c r="C1048">
+        <v>1.7540899999999999</v>
+      </c>
+      <c r="D1048">
+        <v>13.28369</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1049" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B1049">
+        <v>12.962160000000001</v>
+      </c>
+      <c r="C1049">
+        <v>1.89649</v>
+      </c>
+      <c r="D1049">
+        <v>13.197290000000001</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1050" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B1050">
+        <v>12.94839</v>
+      </c>
+      <c r="C1050">
+        <v>1.89164</v>
+      </c>
+      <c r="D1050">
+        <v>13.21062</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1051" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B1051">
+        <v>12.925140000000001</v>
+      </c>
+      <c r="C1051">
+        <v>1.9632700000000001</v>
+      </c>
+      <c r="D1051">
+        <v>13.214259999999999</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
